--- a/ModeloLogico_v2.5.xlsx
+++ b/ModeloLogico_v2.5.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="Hoja2"/>
@@ -625,7 +625,7 @@
       <rPr>
         <b/>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial Nova"/>
         <family val="2"/>
       </rPr>
@@ -634,7 +634,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial Nova"/>
         <family val="2"/>
       </rPr>
@@ -644,7 +644,7 @@
       <rPr>
         <b/>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial Nova"/>
         <family val="2"/>
       </rPr>
@@ -766,7 +766,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial Nova"/>
         <family val="2"/>
       </rPr>
@@ -1447,7 +1447,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1464,7 +1464,7 @@
     <font>
       <b/>
       <sz val="14"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Arial Nova"/>
       <family val="2"/>
     </font>
@@ -1495,22 +1495,10 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial Nova"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFff0000"/>
       <name val="Arial Nova"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos"/>
       <family val="2"/>
     </font>
     <font>
@@ -1527,7 +1515,7 @@
     </font>
     <font>
       <sz val="12"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
@@ -1538,17 +1526,16 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial Nova"/>
-      <family val="2"/>
-    </font>
-    <font>
       <u/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -2017,7 +2004,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="101">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2097,9 +2084,6 @@
     <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf xfId="0" numFmtId="0" borderId="9" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -2112,9 +2096,6 @@
     <xf xfId="0" numFmtId="0" borderId="14" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="14" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf xfId="0" numFmtId="0" borderId="14" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -2127,230 +2108,203 @@
     <xf xfId="0" numFmtId="0" borderId="15" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="16" applyBorder="1" fontId="7" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="16" applyBorder="1" fontId="6" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="8" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="7" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="17" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="17" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="18" applyBorder="1" fontId="7" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="18" applyBorder="1" fontId="6" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="19" applyBorder="1" fontId="5" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="20" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf xfId="0" numFmtId="0" borderId="20" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="19" applyBorder="1" fontId="5" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="6" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf xfId="0" numFmtId="0" borderId="21" applyBorder="1" fontId="5" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf xfId="0" numFmtId="0" borderId="12" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="19" applyBorder="1" fontId="6" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="21" applyBorder="1" fontId="6" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="16" applyBorder="1" fontId="5" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="22" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="12" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="16" applyBorder="1" fontId="6" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="18" applyBorder="1" fontId="6" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="6" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="21" applyBorder="1" fontId="8" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="16" applyBorder="1" fontId="5" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="12" applyBorder="1" fontId="10" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="16" applyBorder="1" fontId="7" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="11" applyBorder="1" fontId="11" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="12" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="23" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="16" applyBorder="1" fontId="6" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="21" applyBorder="1" fontId="7" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="24" applyBorder="1" fontId="5" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="9" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="6" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="25" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="26" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="27" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="17" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="28" applyBorder="1" fontId="5" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="16" applyBorder="1" fontId="6" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="6" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="29" applyBorder="1" fontId="6" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="21" applyBorder="1" fontId="3" applyFont="1" fillId="8" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="12" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="12" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="12" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="6" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="19" applyBorder="1" fontId="7" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="21" applyBorder="1" fontId="7" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="16" applyBorder="1" fontId="5" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="22" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="12" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="16" applyBorder="1" fontId="7" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="18" applyBorder="1" fontId="7" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="9" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="7" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="21" applyBorder="1" fontId="10" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="16" applyBorder="1" fontId="5" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="11" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="12" applyBorder="1" fontId="12" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="16" applyBorder="1" fontId="8" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="11" applyBorder="1" fontId="13" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="12" applyBorder="1" fontId="10" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="23" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="16" applyBorder="1" fontId="7" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="10" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="21" applyBorder="1" fontId="8" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="14" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="24" applyBorder="1" fontId="14" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="21" applyBorder="1" fontId="14" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="9" applyBorder="1" fontId="11" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="7" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="25" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="26" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="10" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="27" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="23" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="17" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="28" applyBorder="1" fontId="14" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="14" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="16" applyBorder="1" fontId="7" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="7" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="16" applyBorder="1" fontId="6" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="29" applyBorder="1" fontId="7" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="11" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="21" applyBorder="1" fontId="3" applyFont="1" fillId="8" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="12" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="15" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
+    <xf xfId="0" numFmtId="0" borderId="30" applyBorder="1" fontId="13" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="31" applyBorder="1" fontId="13" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="30" applyBorder="1" fontId="11" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="32" applyBorder="1" fontId="13" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="30" applyBorder="1" fontId="10" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="30" applyBorder="1" fontId="16" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="14" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="13" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="31" applyBorder="1" fontId="16" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="30" applyBorder="1" fontId="13" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="32" applyBorder="1" fontId="16" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="30" applyBorder="1" fontId="12" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="13" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="11" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="16" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="16" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="13" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2682,2463 +2636,2463 @@
   <dimension ref="A1:P82"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="100" width="59.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="100" width="25.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="100" width="47.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="100" width="12.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="100" width="80.57642857142856" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="100" width="80.57642857142856" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="100" width="71.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="100" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="100" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="100" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="100" width="9.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="100" width="9.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="100" width="15.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="100" width="49.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="100" width="8.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="101" width="137.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="93" width="59.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="93" width="25.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="93" width="47.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="93" width="12.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="93" width="80.57642857142856" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="93" width="80.57642857142856" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="93" width="71.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="93" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="93" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="93" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="93" width="9.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="93" width="9.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="93" width="15.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="93" width="49.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="93" width="8.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="100" width="137.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="102" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A1" s="95" t="s">
         <v>280</v>
       </c>
-      <c r="B1" s="102" t="s">
+      <c r="B1" s="95" t="s">
         <v>281</v>
       </c>
-      <c r="C1" s="102" t="s">
+      <c r="C1" s="95" t="s">
         <v>282</v>
       </c>
-      <c r="D1" s="102" t="s">
+      <c r="D1" s="95" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="102" t="s">
+      <c r="E1" s="95" t="s">
         <v>283</v>
       </c>
-      <c r="F1" s="102" t="s">
+      <c r="F1" s="95" t="s">
         <v>284</v>
       </c>
-      <c r="G1" s="102" t="s">
+      <c r="G1" s="95" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="102" t="s">
+      <c r="H1" s="95" t="s">
         <v>285</v>
       </c>
-      <c r="I1" s="102" t="s">
+      <c r="I1" s="95" t="s">
         <v>286</v>
       </c>
-      <c r="J1" s="102" t="s">
+      <c r="J1" s="95" t="s">
         <v>287</v>
       </c>
-      <c r="K1" s="102" t="s">
+      <c r="K1" s="95" t="s">
         <v>288</v>
       </c>
-      <c r="L1" s="102" t="s">
+      <c r="L1" s="95" t="s">
         <v>289</v>
       </c>
-      <c r="M1" s="102" t="s">
+      <c r="M1" s="95" t="s">
         <v>290</v>
       </c>
-      <c r="N1" s="102" t="s">
+      <c r="N1" s="95" t="s">
         <v>291</v>
       </c>
-      <c r="O1" s="102" t="s">
+      <c r="O1" s="95" t="s">
         <v>292</v>
       </c>
-      <c r="P1" s="108" t="s">
+      <c r="P1" s="96" t="s">
         <v>293</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="102" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A2" s="95" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="102" t="s">
+      <c r="B2" s="95" t="s">
         <v>294</v>
       </c>
-      <c r="C2" s="102"/>
-      <c r="D2" s="102" t="s">
+      <c r="C2" s="95"/>
+      <c r="D2" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E2" s="102" t="s">
+      <c r="E2" s="95" t="s">
         <v>59</v>
       </c>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102" t="s">
+      <c r="F2" s="95"/>
+      <c r="G2" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="H2" s="102"/>
-      <c r="I2" s="102"/>
-      <c r="J2" s="102"/>
-      <c r="K2" s="102"/>
-      <c r="L2" s="102"/>
-      <c r="M2" s="102"/>
-      <c r="N2" s="102"/>
-      <c r="O2" s="102" t="s">
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
+      <c r="O2" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P2" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="102" t="s">
+      <c r="P2" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A3" s="95" t="s">
         <v>296</v>
       </c>
-      <c r="B3" s="102" t="s">
+      <c r="B3" s="95" t="s">
         <v>297</v>
       </c>
-      <c r="C3" s="102"/>
-      <c r="D3" s="102" t="s">
+      <c r="C3" s="95"/>
+      <c r="D3" s="95" t="s">
         <v>298</v>
       </c>
-      <c r="E3" s="102" t="s">
+      <c r="E3" s="95" t="s">
         <v>299</v>
       </c>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102" t="s">
+      <c r="F3" s="95"/>
+      <c r="G3" s="95" t="s">
         <v>300</v>
       </c>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="102"/>
-      <c r="K3" s="102"/>
-      <c r="L3" s="102"/>
-      <c r="M3" s="102"/>
-      <c r="N3" s="102"/>
-      <c r="O3" s="102" t="s">
+      <c r="H3" s="95"/>
+      <c r="I3" s="95"/>
+      <c r="J3" s="95"/>
+      <c r="K3" s="95"/>
+      <c r="L3" s="95"/>
+      <c r="M3" s="95"/>
+      <c r="N3" s="95"/>
+      <c r="O3" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P3" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="102" t="s">
+      <c r="P3" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A4" s="95" t="s">
         <v>109</v>
       </c>
-      <c r="B4" s="102" t="s">
+      <c r="B4" s="95" t="s">
         <v>297</v>
       </c>
-      <c r="C4" s="102"/>
-      <c r="D4" s="102" t="s">
+      <c r="C4" s="95"/>
+      <c r="D4" s="95" t="s">
         <v>249</v>
       </c>
-      <c r="E4" s="102" t="s">
+      <c r="E4" s="95" t="s">
         <v>301</v>
       </c>
-      <c r="F4" s="102"/>
-      <c r="G4" s="102"/>
-      <c r="H4" s="102"/>
-      <c r="I4" s="102"/>
-      <c r="J4" s="102"/>
-      <c r="K4" s="102"/>
-      <c r="L4" s="102"/>
-      <c r="M4" s="102"/>
-      <c r="N4" s="102"/>
-      <c r="O4" s="102" t="s">
+      <c r="F4" s="95"/>
+      <c r="G4" s="95"/>
+      <c r="H4" s="95"/>
+      <c r="I4" s="95"/>
+      <c r="J4" s="95"/>
+      <c r="K4" s="95"/>
+      <c r="L4" s="95"/>
+      <c r="M4" s="95"/>
+      <c r="N4" s="95"/>
+      <c r="O4" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P4" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="102" t="s">
+      <c r="P4" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A5" s="95" t="s">
         <v>114</v>
       </c>
-      <c r="B5" s="102" t="s">
+      <c r="B5" s="95" t="s">
         <v>248</v>
       </c>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102" t="s">
+      <c r="C5" s="95"/>
+      <c r="D5" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E5" s="102" t="s">
+      <c r="E5" s="95" t="s">
         <v>302</v>
       </c>
-      <c r="F5" s="102"/>
-      <c r="G5" s="102" t="s">
+      <c r="F5" s="95"/>
+      <c r="G5" s="95" t="s">
         <v>115</v>
       </c>
-      <c r="H5" s="102"/>
-      <c r="I5" s="102"/>
-      <c r="J5" s="102"/>
-      <c r="K5" s="102"/>
-      <c r="L5" s="102"/>
-      <c r="M5" s="102"/>
-      <c r="N5" s="102"/>
-      <c r="O5" s="102" t="s">
+      <c r="H5" s="95"/>
+      <c r="I5" s="95"/>
+      <c r="J5" s="95"/>
+      <c r="K5" s="95"/>
+      <c r="L5" s="95"/>
+      <c r="M5" s="95"/>
+      <c r="N5" s="95"/>
+      <c r="O5" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P5" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="102" t="s">
+      <c r="P5" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A6" s="95" t="s">
         <v>303</v>
       </c>
-      <c r="B6" s="102" t="s">
+      <c r="B6" s="95" t="s">
         <v>304</v>
       </c>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102" t="s">
+      <c r="C6" s="95"/>
+      <c r="D6" s="95" t="s">
         <v>249</v>
       </c>
-      <c r="E6" s="102" t="s">
+      <c r="E6" s="95" t="s">
         <v>305</v>
       </c>
-      <c r="F6" s="102"/>
-      <c r="G6" s="102" t="s">
+      <c r="F6" s="95"/>
+      <c r="G6" s="95" t="s">
         <v>306</v>
       </c>
-      <c r="H6" s="102"/>
-      <c r="I6" s="102"/>
-      <c r="J6" s="102"/>
-      <c r="K6" s="102"/>
-      <c r="L6" s="102"/>
-      <c r="M6" s="102"/>
-      <c r="N6" s="102"/>
-      <c r="O6" s="102" t="s">
+      <c r="H6" s="95"/>
+      <c r="I6" s="95"/>
+      <c r="J6" s="95"/>
+      <c r="K6" s="95"/>
+      <c r="L6" s="95"/>
+      <c r="M6" s="95"/>
+      <c r="N6" s="95"/>
+      <c r="O6" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P6" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="102" t="s">
+      <c r="P6" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A7" s="95" t="s">
         <v>307</v>
       </c>
-      <c r="B7" s="102" t="s">
+      <c r="B7" s="95" t="s">
         <v>308</v>
       </c>
-      <c r="C7" s="102"/>
-      <c r="D7" s="102" t="s">
+      <c r="C7" s="95"/>
+      <c r="D7" s="95" t="s">
         <v>249</v>
       </c>
-      <c r="E7" s="102" t="s">
+      <c r="E7" s="95" t="s">
         <v>309</v>
       </c>
-      <c r="F7" s="102"/>
-      <c r="G7" s="102"/>
-      <c r="H7" s="102"/>
-      <c r="I7" s="102"/>
-      <c r="J7" s="102"/>
-      <c r="K7" s="102"/>
-      <c r="L7" s="102"/>
-      <c r="M7" s="102"/>
-      <c r="N7" s="102"/>
-      <c r="O7" s="102" t="s">
+      <c r="F7" s="95"/>
+      <c r="G7" s="95"/>
+      <c r="H7" s="95"/>
+      <c r="I7" s="95"/>
+      <c r="J7" s="95"/>
+      <c r="K7" s="95"/>
+      <c r="L7" s="95"/>
+      <c r="M7" s="95"/>
+      <c r="N7" s="95"/>
+      <c r="O7" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P7" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="102" t="s">
+      <c r="P7" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A8" s="95" t="s">
         <v>310</v>
       </c>
-      <c r="B8" s="102" t="s">
+      <c r="B8" s="95" t="s">
         <v>304</v>
       </c>
-      <c r="C8" s="102"/>
-      <c r="D8" s="102" t="s">
+      <c r="C8" s="95"/>
+      <c r="D8" s="95" t="s">
         <v>249</v>
       </c>
-      <c r="E8" s="102" t="s">
+      <c r="E8" s="95" t="s">
         <v>311</v>
       </c>
-      <c r="F8" s="102"/>
-      <c r="G8" s="102"/>
-      <c r="H8" s="102"/>
-      <c r="I8" s="102"/>
-      <c r="J8" s="102"/>
-      <c r="K8" s="102"/>
-      <c r="L8" s="102"/>
-      <c r="M8" s="102"/>
-      <c r="N8" s="102"/>
-      <c r="O8" s="102" t="s">
+      <c r="F8" s="95"/>
+      <c r="G8" s="95"/>
+      <c r="H8" s="95"/>
+      <c r="I8" s="95"/>
+      <c r="J8" s="95"/>
+      <c r="K8" s="95"/>
+      <c r="L8" s="95"/>
+      <c r="M8" s="95"/>
+      <c r="N8" s="95"/>
+      <c r="O8" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P8" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="102" t="s">
+      <c r="P8" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A9" s="95" t="s">
         <v>123</v>
       </c>
-      <c r="B9" s="102" t="s">
+      <c r="B9" s="95" t="s">
         <v>252</v>
       </c>
-      <c r="C9" s="102"/>
-      <c r="D9" s="102" t="s">
+      <c r="C9" s="95"/>
+      <c r="D9" s="95" t="s">
         <v>249</v>
       </c>
-      <c r="E9" s="102" t="s">
+      <c r="E9" s="95" t="s">
         <v>312</v>
       </c>
-      <c r="F9" s="102"/>
-      <c r="G9" s="102" t="s">
+      <c r="F9" s="95"/>
+      <c r="G9" s="95" t="s">
         <v>124</v>
       </c>
-      <c r="H9" s="102"/>
-      <c r="I9" s="102"/>
-      <c r="J9" s="102"/>
-      <c r="K9" s="102"/>
-      <c r="L9" s="102"/>
-      <c r="M9" s="102"/>
-      <c r="N9" s="102"/>
-      <c r="O9" s="102" t="s">
+      <c r="H9" s="95"/>
+      <c r="I9" s="95"/>
+      <c r="J9" s="95"/>
+      <c r="K9" s="95"/>
+      <c r="L9" s="95"/>
+      <c r="M9" s="95"/>
+      <c r="N9" s="95"/>
+      <c r="O9" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P9" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="102" t="s">
+      <c r="P9" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A10" s="95" t="s">
         <v>119</v>
       </c>
-      <c r="B10" s="102" t="s">
+      <c r="B10" s="95" t="s">
         <v>252</v>
       </c>
-      <c r="C10" s="102"/>
-      <c r="D10" s="102" t="s">
+      <c r="C10" s="95"/>
+      <c r="D10" s="95" t="s">
         <v>249</v>
       </c>
-      <c r="E10" s="102" t="s">
+      <c r="E10" s="95" t="s">
         <v>313</v>
       </c>
-      <c r="F10" s="102"/>
-      <c r="G10" s="102" t="s">
+      <c r="F10" s="95"/>
+      <c r="G10" s="95" t="s">
         <v>120</v>
       </c>
-      <c r="H10" s="102"/>
-      <c r="I10" s="102"/>
-      <c r="J10" s="102"/>
-      <c r="K10" s="102"/>
-      <c r="L10" s="102"/>
-      <c r="M10" s="102"/>
-      <c r="N10" s="102"/>
-      <c r="O10" s="102" t="s">
+      <c r="H10" s="95"/>
+      <c r="I10" s="95"/>
+      <c r="J10" s="95"/>
+      <c r="K10" s="95"/>
+      <c r="L10" s="95"/>
+      <c r="M10" s="95"/>
+      <c r="N10" s="95"/>
+      <c r="O10" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P10" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="102" t="s">
+      <c r="P10" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A11" s="95" t="s">
         <v>70</v>
       </c>
-      <c r="B11" s="102" t="s">
+      <c r="B11" s="95" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="102"/>
-      <c r="D11" s="102" t="s">
+      <c r="C11" s="95"/>
+      <c r="D11" s="95" t="s">
         <v>249</v>
       </c>
-      <c r="E11" s="102" t="s">
+      <c r="E11" s="95" t="s">
         <v>315</v>
       </c>
-      <c r="F11" s="102"/>
-      <c r="G11" s="102"/>
-      <c r="H11" s="102"/>
-      <c r="I11" s="102"/>
-      <c r="J11" s="102"/>
-      <c r="K11" s="102"/>
-      <c r="L11" s="102"/>
-      <c r="M11" s="102"/>
-      <c r="N11" s="102"/>
-      <c r="O11" s="102" t="s">
+      <c r="F11" s="95"/>
+      <c r="G11" s="95"/>
+      <c r="H11" s="95"/>
+      <c r="I11" s="95"/>
+      <c r="J11" s="95"/>
+      <c r="K11" s="95"/>
+      <c r="L11" s="95"/>
+      <c r="M11" s="95"/>
+      <c r="N11" s="95"/>
+      <c r="O11" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P11" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="102" t="s">
+      <c r="P11" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A12" s="95" t="s">
         <v>71</v>
       </c>
-      <c r="B12" s="102" t="s">
+      <c r="B12" s="95" t="s">
         <v>260</v>
       </c>
-      <c r="C12" s="102"/>
-      <c r="D12" s="102" t="s">
+      <c r="C12" s="95"/>
+      <c r="D12" s="95" t="s">
         <v>249</v>
       </c>
-      <c r="E12" s="102" t="s">
+      <c r="E12" s="95" t="s">
         <v>316</v>
       </c>
-      <c r="F12" s="102"/>
-      <c r="G12" s="102" t="s">
+      <c r="F12" s="95"/>
+      <c r="G12" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="H12" s="102"/>
-      <c r="I12" s="102"/>
-      <c r="J12" s="102"/>
-      <c r="K12" s="102"/>
-      <c r="L12" s="102"/>
-      <c r="M12" s="102"/>
-      <c r="N12" s="102"/>
-      <c r="O12" s="102" t="s">
+      <c r="H12" s="95"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="95"/>
+      <c r="K12" s="95"/>
+      <c r="L12" s="95"/>
+      <c r="M12" s="95"/>
+      <c r="N12" s="95"/>
+      <c r="O12" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P12" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="102" t="s">
+      <c r="P12" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A13" s="95" t="s">
         <v>74</v>
       </c>
-      <c r="B13" s="102" t="s">
+      <c r="B13" s="95" t="s">
         <v>252</v>
       </c>
-      <c r="C13" s="102"/>
-      <c r="D13" s="102" t="s">
+      <c r="C13" s="95"/>
+      <c r="D13" s="95" t="s">
         <v>249</v>
       </c>
-      <c r="E13" s="102" t="s">
+      <c r="E13" s="95" t="s">
         <v>317</v>
       </c>
-      <c r="F13" s="102"/>
-      <c r="G13" s="102" t="s">
+      <c r="F13" s="95"/>
+      <c r="G13" s="95" t="s">
         <v>75</v>
       </c>
-      <c r="H13" s="102"/>
-      <c r="I13" s="102"/>
-      <c r="J13" s="102"/>
-      <c r="K13" s="102"/>
-      <c r="L13" s="102"/>
-      <c r="M13" s="102"/>
-      <c r="N13" s="102"/>
-      <c r="O13" s="102" t="s">
+      <c r="H13" s="95"/>
+      <c r="I13" s="95"/>
+      <c r="J13" s="95"/>
+      <c r="K13" s="95"/>
+      <c r="L13" s="95"/>
+      <c r="M13" s="95"/>
+      <c r="N13" s="95"/>
+      <c r="O13" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P13" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="102" t="s">
+      <c r="P13" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A14" s="95" t="s">
         <v>318</v>
       </c>
-      <c r="B14" s="102" t="s">
+      <c r="B14" s="95" t="s">
         <v>263</v>
       </c>
-      <c r="C14" s="102" t="s">
+      <c r="C14" s="95" t="s">
         <v>319</v>
       </c>
-      <c r="D14" s="102" t="s">
+      <c r="D14" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E14" s="102" t="s">
+      <c r="E14" s="95" t="s">
         <v>320</v>
       </c>
-      <c r="F14" s="102"/>
-      <c r="G14" s="102" t="s">
+      <c r="F14" s="95"/>
+      <c r="G14" s="95" t="s">
         <v>321</v>
       </c>
-      <c r="H14" s="102" t="s">
+      <c r="H14" s="95" t="s">
         <v>322</v>
       </c>
-      <c r="I14" s="102"/>
-      <c r="J14" s="102"/>
-      <c r="K14" s="102"/>
-      <c r="L14" s="102"/>
-      <c r="M14" s="102"/>
-      <c r="N14" s="102"/>
-      <c r="O14" s="102" t="s">
+      <c r="I14" s="95"/>
+      <c r="J14" s="95"/>
+      <c r="K14" s="95"/>
+      <c r="L14" s="95"/>
+      <c r="M14" s="95"/>
+      <c r="N14" s="95"/>
+      <c r="O14" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P14" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="102" t="s">
+      <c r="P14" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A15" s="95" t="s">
         <v>80</v>
       </c>
-      <c r="B15" s="102" t="s">
+      <c r="B15" s="95" t="s">
         <v>248</v>
       </c>
-      <c r="C15" s="102" t="s">
+      <c r="C15" s="95" t="s">
         <v>323</v>
       </c>
-      <c r="D15" s="102" t="s">
+      <c r="D15" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E15" s="102" t="s">
+      <c r="E15" s="95" t="s">
         <v>324</v>
       </c>
-      <c r="F15" s="102"/>
-      <c r="G15" s="102" t="s">
+      <c r="F15" s="95"/>
+      <c r="G15" s="95" t="s">
         <v>81</v>
       </c>
-      <c r="H15" s="102" t="s">
+      <c r="H15" s="95" t="s">
         <v>325</v>
       </c>
-      <c r="I15" s="102"/>
-      <c r="J15" s="102"/>
-      <c r="K15" s="102"/>
-      <c r="L15" s="102"/>
-      <c r="M15" s="102"/>
-      <c r="N15" s="102"/>
-      <c r="O15" s="102" t="s">
+      <c r="I15" s="95"/>
+      <c r="J15" s="95"/>
+      <c r="K15" s="95"/>
+      <c r="L15" s="95"/>
+      <c r="M15" s="95"/>
+      <c r="N15" s="95"/>
+      <c r="O15" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P15" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="102" t="s">
+      <c r="P15" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A16" s="95" t="s">
         <v>263</v>
       </c>
-      <c r="B16" s="102" t="s">
+      <c r="B16" s="95" t="s">
         <v>248</v>
       </c>
-      <c r="C16" s="102" t="s">
+      <c r="C16" s="95" t="s">
         <v>326</v>
       </c>
-      <c r="D16" s="102" t="s">
+      <c r="D16" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E16" s="102" t="s">
+      <c r="E16" s="95" t="s">
         <v>327</v>
       </c>
-      <c r="F16" s="102"/>
-      <c r="G16" s="102" t="s">
+      <c r="F16" s="95"/>
+      <c r="G16" s="95" t="s">
         <v>328</v>
       </c>
-      <c r="H16" s="102" t="s">
+      <c r="H16" s="95" t="s">
         <v>329</v>
       </c>
-      <c r="I16" s="102"/>
-      <c r="J16" s="102"/>
-      <c r="K16" s="102"/>
-      <c r="L16" s="102"/>
-      <c r="M16" s="102"/>
-      <c r="N16" s="102"/>
-      <c r="O16" s="102" t="s">
+      <c r="I16" s="95"/>
+      <c r="J16" s="95"/>
+      <c r="K16" s="95"/>
+      <c r="L16" s="95"/>
+      <c r="M16" s="95"/>
+      <c r="N16" s="95"/>
+      <c r="O16" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P16" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="102" t="s">
+      <c r="P16" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A17" s="95" t="s">
         <v>330</v>
       </c>
-      <c r="B17" s="102" t="s">
+      <c r="B17" s="95" t="s">
         <v>331</v>
       </c>
-      <c r="C17" s="102"/>
-      <c r="D17" s="102" t="s">
+      <c r="C17" s="95"/>
+      <c r="D17" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E17" s="102" t="s">
+      <c r="E17" s="95" t="s">
         <v>332</v>
       </c>
-      <c r="F17" s="102"/>
-      <c r="G17" s="102" t="s">
+      <c r="F17" s="95"/>
+      <c r="G17" s="95" t="s">
         <v>333</v>
       </c>
-      <c r="H17" s="102"/>
-      <c r="I17" s="102"/>
-      <c r="J17" s="102"/>
-      <c r="K17" s="102"/>
-      <c r="L17" s="102"/>
-      <c r="M17" s="102"/>
-      <c r="N17" s="102"/>
-      <c r="O17" s="102" t="s">
+      <c r="H17" s="95"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="95"/>
+      <c r="K17" s="95"/>
+      <c r="L17" s="95"/>
+      <c r="M17" s="95"/>
+      <c r="N17" s="95"/>
+      <c r="O17" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P17" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="102" t="s">
+      <c r="P17" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A18" s="95" t="s">
         <v>334</v>
       </c>
-      <c r="B18" s="102" t="s">
+      <c r="B18" s="95" t="s">
         <v>331</v>
       </c>
-      <c r="C18" s="102"/>
-      <c r="D18" s="102" t="s">
+      <c r="C18" s="95"/>
+      <c r="D18" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E18" s="102" t="s">
+      <c r="E18" s="95" t="s">
         <v>335</v>
       </c>
-      <c r="F18" s="102"/>
-      <c r="G18" s="102" t="s">
+      <c r="F18" s="95"/>
+      <c r="G18" s="95" t="s">
         <v>336</v>
       </c>
-      <c r="H18" s="102"/>
-      <c r="I18" s="102"/>
-      <c r="J18" s="102"/>
-      <c r="K18" s="102"/>
-      <c r="L18" s="102"/>
-      <c r="M18" s="102"/>
-      <c r="N18" s="102"/>
-      <c r="O18" s="102" t="s">
+      <c r="H18" s="95"/>
+      <c r="I18" s="95"/>
+      <c r="J18" s="95"/>
+      <c r="K18" s="95"/>
+      <c r="L18" s="95"/>
+      <c r="M18" s="95"/>
+      <c r="N18" s="95"/>
+      <c r="O18" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P18" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="102" t="s">
+      <c r="P18" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A19" s="95" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="102" t="s">
+      <c r="B19" s="95" t="s">
         <v>294</v>
       </c>
-      <c r="C19" s="102"/>
-      <c r="D19" s="102" t="s">
+      <c r="C19" s="95"/>
+      <c r="D19" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E19" s="102" t="s">
+      <c r="E19" s="95" t="s">
         <v>337</v>
       </c>
-      <c r="F19" s="102"/>
-      <c r="G19" s="102" t="s">
+      <c r="F19" s="95"/>
+      <c r="G19" s="95" t="s">
         <v>338</v>
       </c>
-      <c r="H19" s="102"/>
-      <c r="I19" s="102"/>
-      <c r="J19" s="102"/>
-      <c r="K19" s="102"/>
-      <c r="L19" s="102"/>
-      <c r="M19" s="102"/>
-      <c r="N19" s="102"/>
-      <c r="O19" s="102" t="s">
+      <c r="H19" s="95"/>
+      <c r="I19" s="95"/>
+      <c r="J19" s="95"/>
+      <c r="K19" s="95"/>
+      <c r="L19" s="95"/>
+      <c r="M19" s="95"/>
+      <c r="N19" s="95"/>
+      <c r="O19" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P19" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="102" t="s">
+      <c r="P19" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A20" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="102" t="s">
+      <c r="B20" s="95" t="s">
         <v>252</v>
       </c>
-      <c r="C20" s="102"/>
-      <c r="D20" s="102" t="s">
+      <c r="C20" s="95"/>
+      <c r="D20" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E20" s="102" t="s">
+      <c r="E20" s="95" t="s">
         <v>339</v>
       </c>
-      <c r="F20" s="102"/>
-      <c r="G20" s="102" t="s">
+      <c r="F20" s="95"/>
+      <c r="G20" s="95" t="s">
         <v>340</v>
       </c>
-      <c r="H20" s="102"/>
-      <c r="I20" s="102"/>
-      <c r="J20" s="102"/>
-      <c r="K20" s="102"/>
-      <c r="L20" s="102"/>
-      <c r="M20" s="102"/>
-      <c r="N20" s="102"/>
-      <c r="O20" s="102" t="s">
+      <c r="H20" s="95"/>
+      <c r="I20" s="95"/>
+      <c r="J20" s="95"/>
+      <c r="K20" s="95"/>
+      <c r="L20" s="95"/>
+      <c r="M20" s="95"/>
+      <c r="N20" s="95"/>
+      <c r="O20" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P20" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="102" t="s">
+      <c r="P20" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A21" s="95" t="s">
         <v>341</v>
       </c>
-      <c r="B21" s="102" t="s">
+      <c r="B21" s="95" t="s">
         <v>342</v>
       </c>
-      <c r="C21" s="102"/>
-      <c r="D21" s="102" t="s">
+      <c r="C21" s="95"/>
+      <c r="D21" s="95" t="s">
         <v>249</v>
       </c>
-      <c r="E21" s="102" t="s">
+      <c r="E21" s="95" t="s">
         <v>343</v>
       </c>
-      <c r="F21" s="102"/>
-      <c r="G21" s="102" t="s">
+      <c r="F21" s="95"/>
+      <c r="G21" s="95" t="s">
         <v>344</v>
       </c>
-      <c r="H21" s="102"/>
-      <c r="I21" s="102"/>
-      <c r="J21" s="102"/>
-      <c r="K21" s="102"/>
-      <c r="L21" s="102"/>
-      <c r="M21" s="102"/>
-      <c r="N21" s="102"/>
-      <c r="O21" s="102" t="s">
+      <c r="H21" s="95"/>
+      <c r="I21" s="95"/>
+      <c r="J21" s="95"/>
+      <c r="K21" s="95"/>
+      <c r="L21" s="95"/>
+      <c r="M21" s="95"/>
+      <c r="N21" s="95"/>
+      <c r="O21" s="95" t="s">
         <v>345</v>
       </c>
-      <c r="P21" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="102" t="s">
+      <c r="P21" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A22" s="95" t="s">
         <v>346</v>
       </c>
-      <c r="B22" s="102" t="s">
+      <c r="B22" s="95" t="s">
         <v>347</v>
       </c>
-      <c r="C22" s="102"/>
-      <c r="D22" s="102" t="s">
+      <c r="C22" s="95"/>
+      <c r="D22" s="95" t="s">
         <v>249</v>
       </c>
-      <c r="E22" s="102" t="s">
+      <c r="E22" s="95" t="s">
         <v>348</v>
       </c>
-      <c r="F22" s="102"/>
-      <c r="G22" s="102" t="s">
+      <c r="F22" s="95"/>
+      <c r="G22" s="95" t="s">
         <v>349</v>
       </c>
-      <c r="H22" s="102"/>
-      <c r="I22" s="102"/>
-      <c r="J22" s="102"/>
-      <c r="K22" s="102"/>
-      <c r="L22" s="102"/>
-      <c r="M22" s="102"/>
-      <c r="N22" s="102"/>
-      <c r="O22" s="102" t="s">
+      <c r="H22" s="95"/>
+      <c r="I22" s="95"/>
+      <c r="J22" s="95"/>
+      <c r="K22" s="95"/>
+      <c r="L22" s="95"/>
+      <c r="M22" s="95"/>
+      <c r="N22" s="95"/>
+      <c r="O22" s="95" t="s">
         <v>345</v>
       </c>
-      <c r="P22" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
-      <c r="A23" s="102" t="s">
+      <c r="P22" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A23" s="95" t="s">
         <v>96</v>
       </c>
-      <c r="B23" s="102" t="s">
+      <c r="B23" s="95" t="s">
         <v>350</v>
       </c>
-      <c r="C23" s="102"/>
-      <c r="D23" s="102" t="s">
+      <c r="C23" s="95"/>
+      <c r="D23" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E23" s="102" t="s">
+      <c r="E23" s="95" t="s">
         <v>351</v>
       </c>
-      <c r="F23" s="102" t="s">
+      <c r="F23" s="95" t="s">
         <v>95</v>
       </c>
-      <c r="G23" s="102" t="s">
+      <c r="G23" s="95" t="s">
         <v>97</v>
       </c>
-      <c r="H23" s="102"/>
-      <c r="I23" s="102"/>
-      <c r="J23" s="102"/>
-      <c r="K23" s="102"/>
-      <c r="L23" s="102"/>
-      <c r="M23" s="102"/>
-      <c r="N23" s="102"/>
-      <c r="O23" s="102" t="s">
+      <c r="H23" s="95"/>
+      <c r="I23" s="95"/>
+      <c r="J23" s="95"/>
+      <c r="K23" s="95"/>
+      <c r="L23" s="95"/>
+      <c r="M23" s="95"/>
+      <c r="N23" s="95"/>
+      <c r="O23" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P23" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="102" t="s">
+      <c r="P23" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A24" s="95" t="s">
         <v>79</v>
       </c>
-      <c r="B24" s="102" t="s">
+      <c r="B24" s="95" t="s">
         <v>252</v>
       </c>
-      <c r="C24" s="102"/>
-      <c r="D24" s="102" t="s">
+      <c r="C24" s="95"/>
+      <c r="D24" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E24" s="102" t="s">
+      <c r="E24" s="95" t="s">
         <v>352</v>
       </c>
-      <c r="F24" s="102"/>
-      <c r="G24" s="102" t="s">
+      <c r="F24" s="95"/>
+      <c r="G24" s="95" t="s">
         <v>353</v>
       </c>
-      <c r="H24" s="102"/>
-      <c r="I24" s="102"/>
-      <c r="J24" s="102"/>
-      <c r="K24" s="102"/>
-      <c r="L24" s="102"/>
-      <c r="M24" s="102"/>
-      <c r="N24" s="102"/>
-      <c r="O24" s="102" t="s">
+      <c r="H24" s="95"/>
+      <c r="I24" s="95"/>
+      <c r="J24" s="95"/>
+      <c r="K24" s="95"/>
+      <c r="L24" s="95"/>
+      <c r="M24" s="95"/>
+      <c r="N24" s="95"/>
+      <c r="O24" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P24" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="102" t="s">
+      <c r="P24" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A25" s="95" t="s">
         <v>354</v>
       </c>
-      <c r="B25" s="102" t="s">
+      <c r="B25" s="95" t="s">
         <v>308</v>
       </c>
-      <c r="C25" s="102"/>
-      <c r="D25" s="102" t="s">
+      <c r="C25" s="95"/>
+      <c r="D25" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E25" s="102" t="s">
+      <c r="E25" s="95" t="s">
         <v>355</v>
       </c>
-      <c r="F25" s="102"/>
-      <c r="G25" s="102"/>
-      <c r="H25" s="102"/>
-      <c r="I25" s="102"/>
-      <c r="J25" s="102"/>
-      <c r="K25" s="102"/>
-      <c r="L25" s="102"/>
-      <c r="M25" s="102"/>
-      <c r="N25" s="102"/>
-      <c r="O25" s="102" t="s">
+      <c r="F25" s="95"/>
+      <c r="G25" s="95"/>
+      <c r="H25" s="95"/>
+      <c r="I25" s="95"/>
+      <c r="J25" s="95"/>
+      <c r="K25" s="95"/>
+      <c r="L25" s="95"/>
+      <c r="M25" s="95"/>
+      <c r="N25" s="95"/>
+      <c r="O25" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P25" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="102" t="s">
+      <c r="P25" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A26" s="95" t="s">
         <v>356</v>
       </c>
-      <c r="B26" s="102" t="s">
+      <c r="B26" s="95" t="s">
         <v>304</v>
       </c>
-      <c r="C26" s="102"/>
-      <c r="D26" s="102" t="s">
+      <c r="C26" s="95"/>
+      <c r="D26" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E26" s="102" t="s">
+      <c r="E26" s="95" t="s">
         <v>357</v>
       </c>
-      <c r="F26" s="102"/>
-      <c r="G26" s="102" t="s">
+      <c r="F26" s="95"/>
+      <c r="G26" s="95" t="s">
         <v>358</v>
       </c>
-      <c r="H26" s="102"/>
-      <c r="I26" s="102"/>
-      <c r="J26" s="102"/>
-      <c r="K26" s="102"/>
-      <c r="L26" s="102"/>
-      <c r="M26" s="102"/>
-      <c r="N26" s="102"/>
-      <c r="O26" s="102" t="s">
+      <c r="H26" s="95"/>
+      <c r="I26" s="95"/>
+      <c r="J26" s="95"/>
+      <c r="K26" s="95"/>
+      <c r="L26" s="95"/>
+      <c r="M26" s="95"/>
+      <c r="N26" s="95"/>
+      <c r="O26" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P26" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="102" t="s">
+      <c r="P26" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A27" s="95" t="s">
         <v>138</v>
       </c>
-      <c r="B27" s="102" t="s">
+      <c r="B27" s="95" t="s">
         <v>260</v>
       </c>
-      <c r="C27" s="102"/>
-      <c r="D27" s="102" t="s">
+      <c r="C27" s="95"/>
+      <c r="D27" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E27" s="102" t="s">
+      <c r="E27" s="95" t="s">
         <v>359</v>
       </c>
-      <c r="F27" s="102"/>
-      <c r="G27" s="102" t="s">
+      <c r="F27" s="95"/>
+      <c r="G27" s="95" t="s">
         <v>132</v>
       </c>
-      <c r="H27" s="102"/>
-      <c r="I27" s="102"/>
-      <c r="J27" s="102"/>
-      <c r="K27" s="102"/>
-      <c r="L27" s="102"/>
-      <c r="M27" s="102"/>
-      <c r="N27" s="102"/>
-      <c r="O27" s="102" t="s">
+      <c r="H27" s="95"/>
+      <c r="I27" s="95"/>
+      <c r="J27" s="95"/>
+      <c r="K27" s="95"/>
+      <c r="L27" s="95"/>
+      <c r="M27" s="95"/>
+      <c r="N27" s="95"/>
+      <c r="O27" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P27" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
-      <c r="A28" s="102" t="s">
+      <c r="P27" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A28" s="95" t="s">
         <v>135</v>
       </c>
-      <c r="B28" s="102" t="s">
+      <c r="B28" s="95" t="s">
         <v>252</v>
       </c>
-      <c r="C28" s="102"/>
-      <c r="D28" s="102" t="s">
+      <c r="C28" s="95"/>
+      <c r="D28" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E28" s="102" t="s">
+      <c r="E28" s="95" t="s">
         <v>360</v>
       </c>
-      <c r="F28" s="102"/>
-      <c r="G28" s="102" t="s">
+      <c r="F28" s="95"/>
+      <c r="G28" s="95" t="s">
         <v>120</v>
       </c>
-      <c r="H28" s="102"/>
-      <c r="I28" s="102"/>
-      <c r="J28" s="102"/>
-      <c r="K28" s="102"/>
-      <c r="L28" s="102"/>
-      <c r="M28" s="102"/>
-      <c r="N28" s="102"/>
-      <c r="O28" s="102" t="s">
+      <c r="H28" s="95"/>
+      <c r="I28" s="95"/>
+      <c r="J28" s="95"/>
+      <c r="K28" s="95"/>
+      <c r="L28" s="95"/>
+      <c r="M28" s="95"/>
+      <c r="N28" s="95"/>
+      <c r="O28" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P28" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
-      <c r="A29" s="102" t="s">
+      <c r="P28" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A29" s="95" t="s">
         <v>361</v>
       </c>
-      <c r="B29" s="102" t="s">
+      <c r="B29" s="95" t="s">
         <v>314</v>
       </c>
-      <c r="C29" s="102"/>
-      <c r="D29" s="102" t="s">
+      <c r="C29" s="95"/>
+      <c r="D29" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E29" s="102" t="s">
+      <c r="E29" s="95" t="s">
         <v>83</v>
       </c>
-      <c r="F29" s="102"/>
-      <c r="G29" s="102"/>
-      <c r="H29" s="102"/>
-      <c r="I29" s="102"/>
-      <c r="J29" s="102"/>
-      <c r="K29" s="102"/>
-      <c r="L29" s="102"/>
-      <c r="M29" s="102"/>
-      <c r="N29" s="102"/>
-      <c r="O29" s="102" t="s">
+      <c r="F29" s="95"/>
+      <c r="G29" s="95"/>
+      <c r="H29" s="95"/>
+      <c r="I29" s="95"/>
+      <c r="J29" s="95"/>
+      <c r="K29" s="95"/>
+      <c r="L29" s="95"/>
+      <c r="M29" s="95"/>
+      <c r="N29" s="95"/>
+      <c r="O29" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P29" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
-      <c r="A30" s="102" t="s">
+      <c r="P29" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A30" s="95" t="s">
         <v>362</v>
       </c>
-      <c r="B30" s="102" t="s">
+      <c r="B30" s="95" t="s">
         <v>260</v>
       </c>
-      <c r="C30" s="102"/>
-      <c r="D30" s="102" t="s">
+      <c r="C30" s="95"/>
+      <c r="D30" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E30" s="102" t="s">
+      <c r="E30" s="95" t="s">
         <v>363</v>
       </c>
-      <c r="F30" s="102"/>
-      <c r="G30" s="102" t="s">
+      <c r="F30" s="95"/>
+      <c r="G30" s="95" t="s">
         <v>85</v>
       </c>
-      <c r="H30" s="102"/>
-      <c r="I30" s="102"/>
-      <c r="J30" s="102"/>
-      <c r="K30" s="102"/>
-      <c r="L30" s="102"/>
-      <c r="M30" s="102"/>
-      <c r="N30" s="102"/>
-      <c r="O30" s="102" t="s">
+      <c r="H30" s="95"/>
+      <c r="I30" s="95"/>
+      <c r="J30" s="95"/>
+      <c r="K30" s="95"/>
+      <c r="L30" s="95"/>
+      <c r="M30" s="95"/>
+      <c r="N30" s="95"/>
+      <c r="O30" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P30" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
-      <c r="A31" s="102" t="s">
+      <c r="P30" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A31" s="95" t="s">
         <v>364</v>
       </c>
-      <c r="B31" s="102" t="s">
+      <c r="B31" s="95" t="s">
         <v>252</v>
       </c>
-      <c r="C31" s="102"/>
-      <c r="D31" s="102" t="s">
+      <c r="C31" s="95"/>
+      <c r="D31" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E31" s="102" t="s">
+      <c r="E31" s="95" t="s">
         <v>365</v>
       </c>
-      <c r="F31" s="102"/>
-      <c r="G31" s="102" t="s">
+      <c r="F31" s="95"/>
+      <c r="G31" s="95" t="s">
         <v>75</v>
       </c>
-      <c r="H31" s="102"/>
-      <c r="I31" s="102"/>
-      <c r="J31" s="102"/>
-      <c r="K31" s="102"/>
-      <c r="L31" s="102"/>
-      <c r="M31" s="102"/>
-      <c r="N31" s="102"/>
-      <c r="O31" s="102" t="s">
+      <c r="H31" s="95"/>
+      <c r="I31" s="95"/>
+      <c r="J31" s="95"/>
+      <c r="K31" s="95"/>
+      <c r="L31" s="95"/>
+      <c r="M31" s="95"/>
+      <c r="N31" s="95"/>
+      <c r="O31" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P31" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
-      <c r="A32" s="102" t="s">
+      <c r="P31" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A32" s="95" t="s">
         <v>366</v>
       </c>
-      <c r="B32" s="102" t="s">
+      <c r="B32" s="95" t="s">
         <v>304</v>
       </c>
-      <c r="C32" s="102"/>
-      <c r="D32" s="102" t="s">
+      <c r="C32" s="95"/>
+      <c r="D32" s="95" t="s">
         <v>298</v>
       </c>
-      <c r="E32" s="102" t="s">
+      <c r="E32" s="95" t="s">
         <v>367</v>
       </c>
-      <c r="F32" s="102"/>
-      <c r="G32" s="102" t="s">
+      <c r="F32" s="95"/>
+      <c r="G32" s="95" t="s">
         <v>368</v>
       </c>
-      <c r="H32" s="102"/>
-      <c r="I32" s="102"/>
-      <c r="J32" s="102"/>
-      <c r="K32" s="102"/>
-      <c r="L32" s="102"/>
-      <c r="M32" s="102"/>
-      <c r="N32" s="102"/>
-      <c r="O32" s="102" t="s">
+      <c r="H32" s="95"/>
+      <c r="I32" s="95"/>
+      <c r="J32" s="95"/>
+      <c r="K32" s="95"/>
+      <c r="L32" s="95"/>
+      <c r="M32" s="95"/>
+      <c r="N32" s="95"/>
+      <c r="O32" s="95" t="s">
         <v>345</v>
       </c>
-      <c r="P32" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
-      <c r="A33" s="102" t="s">
+      <c r="P32" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A33" s="95" t="s">
         <v>369</v>
       </c>
-      <c r="B33" s="102" t="s">
+      <c r="B33" s="95" t="s">
         <v>370</v>
       </c>
-      <c r="C33" s="102"/>
-      <c r="D33" s="102" t="s">
+      <c r="C33" s="95"/>
+      <c r="D33" s="95" t="s">
         <v>371</v>
       </c>
-      <c r="E33" s="102" t="s">
+      <c r="E33" s="95" t="s">
         <v>372</v>
       </c>
-      <c r="F33" s="102"/>
-      <c r="G33" s="102" t="s">
+      <c r="F33" s="95"/>
+      <c r="G33" s="95" t="s">
         <v>373</v>
       </c>
-      <c r="H33" s="102"/>
-      <c r="I33" s="102"/>
-      <c r="J33" s="102"/>
-      <c r="K33" s="102"/>
-      <c r="L33" s="102"/>
-      <c r="M33" s="102"/>
-      <c r="N33" s="102"/>
-      <c r="O33" s="102" t="s">
+      <c r="H33" s="95"/>
+      <c r="I33" s="95"/>
+      <c r="J33" s="95"/>
+      <c r="K33" s="95"/>
+      <c r="L33" s="95"/>
+      <c r="M33" s="95"/>
+      <c r="N33" s="95"/>
+      <c r="O33" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P33" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
-      <c r="A34" s="102" t="s">
+      <c r="P33" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A34" s="95" t="s">
         <v>104</v>
       </c>
-      <c r="B34" s="102" t="s">
+      <c r="B34" s="95" t="s">
         <v>252</v>
       </c>
-      <c r="C34" s="102"/>
-      <c r="D34" s="102" t="s">
+      <c r="C34" s="95"/>
+      <c r="D34" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E34" s="102" t="s">
+      <c r="E34" s="95" t="s">
         <v>374</v>
       </c>
-      <c r="F34" s="102"/>
-      <c r="G34" s="102" t="s">
+      <c r="F34" s="95"/>
+      <c r="G34" s="95" t="s">
         <v>105</v>
       </c>
-      <c r="H34" s="102"/>
-      <c r="I34" s="102"/>
-      <c r="J34" s="102"/>
-      <c r="K34" s="102"/>
-      <c r="L34" s="102"/>
-      <c r="M34" s="102"/>
-      <c r="N34" s="102"/>
-      <c r="O34" s="102" t="s">
+      <c r="H34" s="95"/>
+      <c r="I34" s="95"/>
+      <c r="J34" s="95"/>
+      <c r="K34" s="95"/>
+      <c r="L34" s="95"/>
+      <c r="M34" s="95"/>
+      <c r="N34" s="95"/>
+      <c r="O34" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P34" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
-      <c r="A35" s="102" t="s">
+      <c r="P34" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A35" s="95" t="s">
         <v>375</v>
       </c>
-      <c r="B35" s="102" t="s">
+      <c r="B35" s="95" t="s">
         <v>252</v>
       </c>
-      <c r="C35" s="102"/>
-      <c r="D35" s="102" t="s">
+      <c r="C35" s="95"/>
+      <c r="D35" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E35" s="102" t="s">
+      <c r="E35" s="95" t="s">
         <v>376</v>
       </c>
-      <c r="F35" s="102"/>
-      <c r="G35" s="102" t="s">
+      <c r="F35" s="95"/>
+      <c r="G35" s="95" t="s">
         <v>132</v>
       </c>
-      <c r="H35" s="102"/>
-      <c r="I35" s="102"/>
-      <c r="J35" s="102"/>
-      <c r="K35" s="102"/>
-      <c r="L35" s="102"/>
-      <c r="M35" s="102"/>
-      <c r="N35" s="102"/>
-      <c r="O35" s="102" t="s">
+      <c r="H35" s="95"/>
+      <c r="I35" s="95"/>
+      <c r="J35" s="95"/>
+      <c r="K35" s="95"/>
+      <c r="L35" s="95"/>
+      <c r="M35" s="95"/>
+      <c r="N35" s="95"/>
+      <c r="O35" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P35" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
-      <c r="A36" s="102" t="s">
+      <c r="P35" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A36" s="95" t="s">
         <v>377</v>
       </c>
-      <c r="B36" s="102" t="s">
+      <c r="B36" s="95" t="s">
         <v>308</v>
       </c>
-      <c r="C36" s="102"/>
-      <c r="D36" s="102" t="s">
+      <c r="C36" s="95"/>
+      <c r="D36" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E36" s="102" t="s">
+      <c r="E36" s="95" t="s">
         <v>378</v>
       </c>
-      <c r="F36" s="102"/>
-      <c r="G36" s="102"/>
-      <c r="H36" s="102"/>
-      <c r="I36" s="102"/>
-      <c r="J36" s="102"/>
-      <c r="K36" s="102"/>
-      <c r="L36" s="102"/>
-      <c r="M36" s="102"/>
-      <c r="N36" s="102"/>
-      <c r="O36" s="102" t="s">
+      <c r="F36" s="95"/>
+      <c r="G36" s="95"/>
+      <c r="H36" s="95"/>
+      <c r="I36" s="95"/>
+      <c r="J36" s="95"/>
+      <c r="K36" s="95"/>
+      <c r="L36" s="95"/>
+      <c r="M36" s="95"/>
+      <c r="N36" s="95"/>
+      <c r="O36" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P36" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
-      <c r="A37" s="102" t="s">
+      <c r="P36" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A37" s="95" t="s">
         <v>379</v>
       </c>
-      <c r="B37" s="102" t="s">
+      <c r="B37" s="95" t="s">
         <v>304</v>
       </c>
-      <c r="C37" s="102"/>
-      <c r="D37" s="102" t="s">
+      <c r="C37" s="95"/>
+      <c r="D37" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E37" s="102" t="s">
+      <c r="E37" s="95" t="s">
         <v>380</v>
       </c>
-      <c r="F37" s="102"/>
-      <c r="G37" s="102"/>
-      <c r="H37" s="102"/>
-      <c r="I37" s="102"/>
-      <c r="J37" s="102"/>
-      <c r="K37" s="102"/>
-      <c r="L37" s="102"/>
-      <c r="M37" s="102"/>
-      <c r="N37" s="102"/>
-      <c r="O37" s="102" t="s">
+      <c r="F37" s="95"/>
+      <c r="G37" s="95"/>
+      <c r="H37" s="95"/>
+      <c r="I37" s="95"/>
+      <c r="J37" s="95"/>
+      <c r="K37" s="95"/>
+      <c r="L37" s="95"/>
+      <c r="M37" s="95"/>
+      <c r="N37" s="95"/>
+      <c r="O37" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P37" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
-      <c r="A38" s="102" t="s">
+      <c r="P37" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A38" s="95" t="s">
         <v>381</v>
       </c>
-      <c r="B38" s="102" t="s">
+      <c r="B38" s="95" t="s">
         <v>252</v>
       </c>
-      <c r="C38" s="102"/>
-      <c r="D38" s="102" t="s">
+      <c r="C38" s="95"/>
+      <c r="D38" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E38" s="102" t="s">
+      <c r="E38" s="95" t="s">
         <v>382</v>
       </c>
-      <c r="F38" s="102"/>
-      <c r="G38" s="102" t="s">
+      <c r="F38" s="95"/>
+      <c r="G38" s="95" t="s">
         <v>132</v>
       </c>
-      <c r="H38" s="102"/>
-      <c r="I38" s="102"/>
-      <c r="J38" s="102"/>
-      <c r="K38" s="102"/>
-      <c r="L38" s="102"/>
-      <c r="M38" s="102"/>
-      <c r="N38" s="102"/>
-      <c r="O38" s="102" t="s">
+      <c r="H38" s="95"/>
+      <c r="I38" s="95"/>
+      <c r="J38" s="95"/>
+      <c r="K38" s="95"/>
+      <c r="L38" s="95"/>
+      <c r="M38" s="95"/>
+      <c r="N38" s="95"/>
+      <c r="O38" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P38" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
-      <c r="A39" s="102" t="s">
+      <c r="P38" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A39" s="95" t="s">
         <v>383</v>
       </c>
-      <c r="B39" s="102" t="s">
+      <c r="B39" s="95" t="s">
         <v>252</v>
       </c>
-      <c r="C39" s="102"/>
-      <c r="D39" s="102" t="s">
+      <c r="C39" s="95"/>
+      <c r="D39" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E39" s="102" t="s">
+      <c r="E39" s="95" t="s">
         <v>384</v>
       </c>
-      <c r="F39" s="102"/>
-      <c r="G39" s="102" t="s">
+      <c r="F39" s="95"/>
+      <c r="G39" s="95" t="s">
         <v>120</v>
       </c>
-      <c r="H39" s="102"/>
-      <c r="I39" s="102"/>
-      <c r="J39" s="102"/>
-      <c r="K39" s="102"/>
-      <c r="L39" s="102"/>
-      <c r="M39" s="102"/>
-      <c r="N39" s="102"/>
-      <c r="O39" s="102" t="s">
+      <c r="H39" s="95"/>
+      <c r="I39" s="95"/>
+      <c r="J39" s="95"/>
+      <c r="K39" s="95"/>
+      <c r="L39" s="95"/>
+      <c r="M39" s="95"/>
+      <c r="N39" s="95"/>
+      <c r="O39" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P39" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
-      <c r="A40" s="102" t="s">
+      <c r="P39" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A40" s="95" t="s">
         <v>385</v>
       </c>
-      <c r="B40" s="102" t="s">
+      <c r="B40" s="95" t="s">
         <v>314</v>
       </c>
-      <c r="C40" s="102"/>
-      <c r="D40" s="102" t="s">
+      <c r="C40" s="95"/>
+      <c r="D40" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E40" s="102" t="s">
+      <c r="E40" s="95" t="s">
         <v>386</v>
       </c>
-      <c r="F40" s="102"/>
-      <c r="G40" s="102"/>
-      <c r="H40" s="102"/>
-      <c r="I40" s="102"/>
-      <c r="J40" s="102"/>
-      <c r="K40" s="102"/>
-      <c r="L40" s="102"/>
-      <c r="M40" s="102"/>
-      <c r="N40" s="102"/>
-      <c r="O40" s="102" t="s">
+      <c r="F40" s="95"/>
+      <c r="G40" s="95"/>
+      <c r="H40" s="95"/>
+      <c r="I40" s="95"/>
+      <c r="J40" s="95"/>
+      <c r="K40" s="95"/>
+      <c r="L40" s="95"/>
+      <c r="M40" s="95"/>
+      <c r="N40" s="95"/>
+      <c r="O40" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P40" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
-      <c r="A41" s="102" t="s">
+      <c r="P40" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A41" s="95" t="s">
         <v>387</v>
       </c>
-      <c r="B41" s="102" t="s">
+      <c r="B41" s="95" t="s">
         <v>252</v>
       </c>
-      <c r="C41" s="102"/>
-      <c r="D41" s="102" t="s">
+      <c r="C41" s="95"/>
+      <c r="D41" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E41" s="102" t="s">
+      <c r="E41" s="95" t="s">
         <v>388</v>
       </c>
-      <c r="F41" s="102"/>
-      <c r="G41" s="102" t="s">
+      <c r="F41" s="95"/>
+      <c r="G41" s="95" t="s">
         <v>85</v>
       </c>
-      <c r="H41" s="102"/>
-      <c r="I41" s="102"/>
-      <c r="J41" s="102"/>
-      <c r="K41" s="102"/>
-      <c r="L41" s="102"/>
-      <c r="M41" s="102"/>
-      <c r="N41" s="102"/>
-      <c r="O41" s="102" t="s">
+      <c r="H41" s="95"/>
+      <c r="I41" s="95"/>
+      <c r="J41" s="95"/>
+      <c r="K41" s="95"/>
+      <c r="L41" s="95"/>
+      <c r="M41" s="95"/>
+      <c r="N41" s="95"/>
+      <c r="O41" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P41" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
-      <c r="A42" s="102" t="s">
+      <c r="P41" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A42" s="95" t="s">
         <v>389</v>
       </c>
-      <c r="B42" s="102" t="s">
+      <c r="B42" s="95" t="s">
         <v>252</v>
       </c>
-      <c r="C42" s="102"/>
-      <c r="D42" s="102" t="s">
+      <c r="C42" s="95"/>
+      <c r="D42" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E42" s="102" t="s">
+      <c r="E42" s="95" t="s">
         <v>390</v>
       </c>
-      <c r="F42" s="102"/>
-      <c r="G42" s="102" t="s">
+      <c r="F42" s="95"/>
+      <c r="G42" s="95" t="s">
         <v>75</v>
       </c>
-      <c r="H42" s="102"/>
-      <c r="I42" s="102"/>
-      <c r="J42" s="102"/>
-      <c r="K42" s="102"/>
-      <c r="L42" s="102"/>
-      <c r="M42" s="102"/>
-      <c r="N42" s="102"/>
-      <c r="O42" s="102" t="s">
+      <c r="H42" s="95"/>
+      <c r="I42" s="95"/>
+      <c r="J42" s="95"/>
+      <c r="K42" s="95"/>
+      <c r="L42" s="95"/>
+      <c r="M42" s="95"/>
+      <c r="N42" s="95"/>
+      <c r="O42" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P42" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
-      <c r="A43" s="102" t="s">
+      <c r="P42" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A43" s="95" t="s">
         <v>88</v>
       </c>
-      <c r="B43" s="102" t="s">
+      <c r="B43" s="95" t="s">
         <v>391</v>
       </c>
-      <c r="C43" s="102"/>
-      <c r="D43" s="102" t="s">
+      <c r="C43" s="95"/>
+      <c r="D43" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E43" s="102" t="s">
+      <c r="E43" s="95" t="s">
         <v>392</v>
       </c>
-      <c r="F43" s="102"/>
-      <c r="G43" s="102"/>
-      <c r="H43" s="102"/>
-      <c r="I43" s="102"/>
-      <c r="J43" s="102"/>
-      <c r="K43" s="102"/>
-      <c r="L43" s="102"/>
-      <c r="M43" s="102"/>
-      <c r="N43" s="102"/>
-      <c r="O43" s="102" t="s">
+      <c r="F43" s="95"/>
+      <c r="G43" s="95"/>
+      <c r="H43" s="95"/>
+      <c r="I43" s="95"/>
+      <c r="J43" s="95"/>
+      <c r="K43" s="95"/>
+      <c r="L43" s="95"/>
+      <c r="M43" s="95"/>
+      <c r="N43" s="95"/>
+      <c r="O43" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P43" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
-      <c r="A44" s="102" t="s">
+      <c r="P43" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A44" s="95" t="s">
         <v>156</v>
       </c>
-      <c r="B44" s="102" t="s">
+      <c r="B44" s="95" t="s">
         <v>248</v>
       </c>
-      <c r="C44" s="102"/>
-      <c r="D44" s="102" t="s">
+      <c r="C44" s="95"/>
+      <c r="D44" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E44" s="102" t="s">
+      <c r="E44" s="95" t="s">
         <v>393</v>
       </c>
-      <c r="F44" s="102"/>
-      <c r="G44" s="102"/>
-      <c r="H44" s="102"/>
-      <c r="I44" s="102"/>
-      <c r="J44" s="102"/>
-      <c r="K44" s="102"/>
-      <c r="L44" s="102"/>
-      <c r="M44" s="102"/>
-      <c r="N44" s="102"/>
-      <c r="O44" s="102" t="s">
+      <c r="F44" s="95"/>
+      <c r="G44" s="95"/>
+      <c r="H44" s="95"/>
+      <c r="I44" s="95"/>
+      <c r="J44" s="95"/>
+      <c r="K44" s="95"/>
+      <c r="L44" s="95"/>
+      <c r="M44" s="95"/>
+      <c r="N44" s="95"/>
+      <c r="O44" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P44" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
-      <c r="A45" s="102" t="s">
+      <c r="P44" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A45" s="95" t="s">
         <v>394</v>
       </c>
-      <c r="B45" s="102" t="s">
+      <c r="B45" s="95" t="s">
         <v>248</v>
       </c>
-      <c r="C45" s="102"/>
-      <c r="D45" s="102" t="s">
+      <c r="C45" s="95"/>
+      <c r="D45" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E45" s="102" t="s">
+      <c r="E45" s="95" t="s">
         <v>395</v>
       </c>
-      <c r="F45" s="102"/>
-      <c r="G45" s="102"/>
-      <c r="H45" s="102"/>
-      <c r="I45" s="102"/>
-      <c r="J45" s="102"/>
-      <c r="K45" s="102"/>
-      <c r="L45" s="102"/>
-      <c r="M45" s="102"/>
-      <c r="N45" s="102"/>
-      <c r="O45" s="102" t="s">
+      <c r="F45" s="95"/>
+      <c r="G45" s="95"/>
+      <c r="H45" s="95"/>
+      <c r="I45" s="95"/>
+      <c r="J45" s="95"/>
+      <c r="K45" s="95"/>
+      <c r="L45" s="95"/>
+      <c r="M45" s="95"/>
+      <c r="N45" s="95"/>
+      <c r="O45" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P45" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
-      <c r="A46" s="102" t="s">
+      <c r="P45" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A46" s="95" t="s">
         <v>92</v>
       </c>
-      <c r="B46" s="102" t="s">
+      <c r="B46" s="95" t="s">
         <v>391</v>
       </c>
-      <c r="C46" s="102"/>
-      <c r="D46" s="102" t="s">
+      <c r="C46" s="95"/>
+      <c r="D46" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E46" s="102" t="s">
+      <c r="E46" s="95" t="s">
         <v>91</v>
       </c>
-      <c r="F46" s="102"/>
-      <c r="G46" s="102" t="s">
+      <c r="F46" s="95"/>
+      <c r="G46" s="95" t="s">
         <v>93</v>
       </c>
-      <c r="H46" s="102"/>
-      <c r="I46" s="102"/>
-      <c r="J46" s="102"/>
-      <c r="K46" s="102"/>
-      <c r="L46" s="102"/>
-      <c r="M46" s="102"/>
-      <c r="N46" s="102"/>
-      <c r="O46" s="102" t="s">
+      <c r="H46" s="95"/>
+      <c r="I46" s="95"/>
+      <c r="J46" s="95"/>
+      <c r="K46" s="95"/>
+      <c r="L46" s="95"/>
+      <c r="M46" s="95"/>
+      <c r="N46" s="95"/>
+      <c r="O46" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P46" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
-      <c r="A47" s="102" t="s">
+      <c r="P46" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A47" s="95" t="s">
         <v>396</v>
       </c>
-      <c r="B47" s="102" t="s">
+      <c r="B47" s="95" t="s">
         <v>397</v>
       </c>
-      <c r="C47" s="102"/>
-      <c r="D47" s="102" t="s">
+      <c r="C47" s="95"/>
+      <c r="D47" s="95" t="s">
         <v>298</v>
       </c>
-      <c r="E47" s="102" t="s">
+      <c r="E47" s="95" t="s">
         <v>398</v>
       </c>
-      <c r="F47" s="102"/>
-      <c r="G47" s="102" t="s">
+      <c r="F47" s="95"/>
+      <c r="G47" s="95" t="s">
         <v>399</v>
       </c>
-      <c r="H47" s="102"/>
-      <c r="I47" s="102"/>
-      <c r="J47" s="102"/>
-      <c r="K47" s="102"/>
-      <c r="L47" s="102"/>
-      <c r="M47" s="102"/>
-      <c r="N47" s="102"/>
-      <c r="O47" s="102" t="s">
+      <c r="H47" s="95"/>
+      <c r="I47" s="95"/>
+      <c r="J47" s="95"/>
+      <c r="K47" s="95"/>
+      <c r="L47" s="95"/>
+      <c r="M47" s="95"/>
+      <c r="N47" s="95"/>
+      <c r="O47" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P47" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
-      <c r="A48" s="102" t="s">
+      <c r="P47" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A48" s="95" t="s">
         <v>400</v>
       </c>
-      <c r="B48" s="102" t="s">
+      <c r="B48" s="95" t="s">
         <v>252</v>
       </c>
-      <c r="C48" s="102"/>
-      <c r="D48" s="102" t="s">
+      <c r="C48" s="95"/>
+      <c r="D48" s="95" t="s">
         <v>249</v>
       </c>
-      <c r="E48" s="102"/>
-      <c r="F48" s="102"/>
-      <c r="G48" s="102"/>
-      <c r="H48" s="102"/>
-      <c r="I48" s="102"/>
-      <c r="J48" s="102"/>
-      <c r="K48" s="102"/>
-      <c r="L48" s="102"/>
-      <c r="M48" s="102"/>
-      <c r="N48" s="102"/>
-      <c r="O48" s="102" t="s">
+      <c r="E48" s="95"/>
+      <c r="F48" s="95"/>
+      <c r="G48" s="95"/>
+      <c r="H48" s="95"/>
+      <c r="I48" s="95"/>
+      <c r="J48" s="95"/>
+      <c r="K48" s="95"/>
+      <c r="L48" s="95"/>
+      <c r="M48" s="95"/>
+      <c r="N48" s="95"/>
+      <c r="O48" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P48" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
-      <c r="A49" s="102" t="s">
+      <c r="P48" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A49" s="95" t="s">
         <v>228</v>
       </c>
-      <c r="B49" s="102" t="s">
+      <c r="B49" s="95" t="s">
         <v>397</v>
       </c>
-      <c r="C49" s="102"/>
-      <c r="D49" s="102" t="s">
+      <c r="C49" s="95"/>
+      <c r="D49" s="95" t="s">
         <v>249</v>
       </c>
-      <c r="E49" s="102" t="s">
+      <c r="E49" s="95" t="s">
         <v>225</v>
       </c>
-      <c r="F49" s="102"/>
-      <c r="G49" s="102" t="s">
+      <c r="F49" s="95"/>
+      <c r="G49" s="95" t="s">
         <v>229</v>
       </c>
-      <c r="H49" s="102"/>
-      <c r="I49" s="102"/>
-      <c r="J49" s="102"/>
-      <c r="K49" s="102"/>
-      <c r="L49" s="102"/>
-      <c r="M49" s="102"/>
-      <c r="N49" s="102"/>
-      <c r="O49" s="102" t="s">
+      <c r="H49" s="95"/>
+      <c r="I49" s="95"/>
+      <c r="J49" s="95"/>
+      <c r="K49" s="95"/>
+      <c r="L49" s="95"/>
+      <c r="M49" s="95"/>
+      <c r="N49" s="95"/>
+      <c r="O49" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P49" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
-      <c r="A50" s="102" t="s">
+      <c r="P49" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A50" s="95" t="s">
         <v>234</v>
       </c>
-      <c r="B50" s="102" t="s">
+      <c r="B50" s="95" t="s">
         <v>397</v>
       </c>
-      <c r="C50" s="102"/>
-      <c r="D50" s="102" t="s">
+      <c r="C50" s="95"/>
+      <c r="D50" s="95" t="s">
         <v>249</v>
       </c>
-      <c r="E50" s="102" t="s">
+      <c r="E50" s="95" t="s">
         <v>232</v>
       </c>
-      <c r="F50" s="102"/>
-      <c r="G50" s="102" t="s">
+      <c r="F50" s="95"/>
+      <c r="G50" s="95" t="s">
         <v>229</v>
       </c>
-      <c r="H50" s="102"/>
-      <c r="I50" s="102"/>
-      <c r="J50" s="102"/>
-      <c r="K50" s="102"/>
-      <c r="L50" s="102"/>
-      <c r="M50" s="102"/>
-      <c r="N50" s="102"/>
-      <c r="O50" s="102" t="s">
+      <c r="H50" s="95"/>
+      <c r="I50" s="95"/>
+      <c r="J50" s="95"/>
+      <c r="K50" s="95"/>
+      <c r="L50" s="95"/>
+      <c r="M50" s="95"/>
+      <c r="N50" s="95"/>
+      <c r="O50" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P50" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
-      <c r="A51" s="102" t="s">
+      <c r="P50" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A51" s="95" t="s">
         <v>238</v>
       </c>
-      <c r="B51" s="102" t="s">
+      <c r="B51" s="95" t="s">
         <v>397</v>
       </c>
-      <c r="C51" s="102"/>
-      <c r="D51" s="102" t="s">
+      <c r="C51" s="95"/>
+      <c r="D51" s="95" t="s">
         <v>249</v>
       </c>
-      <c r="E51" s="102" t="s">
+      <c r="E51" s="95" t="s">
         <v>236</v>
       </c>
-      <c r="F51" s="102"/>
-      <c r="G51" s="102" t="s">
+      <c r="F51" s="95"/>
+      <c r="G51" s="95" t="s">
         <v>229</v>
       </c>
-      <c r="H51" s="102"/>
-      <c r="I51" s="102"/>
-      <c r="J51" s="102"/>
-      <c r="K51" s="102"/>
-      <c r="L51" s="102"/>
-      <c r="M51" s="102"/>
-      <c r="N51" s="102"/>
-      <c r="O51" s="102" t="s">
+      <c r="H51" s="95"/>
+      <c r="I51" s="95"/>
+      <c r="J51" s="95"/>
+      <c r="K51" s="95"/>
+      <c r="L51" s="95"/>
+      <c r="M51" s="95"/>
+      <c r="N51" s="95"/>
+      <c r="O51" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P51" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
-      <c r="A52" s="102" t="s">
+      <c r="P51" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A52" s="95" t="s">
         <v>141</v>
       </c>
-      <c r="B52" s="102" t="s">
+      <c r="B52" s="95" t="s">
         <v>252</v>
       </c>
-      <c r="C52" s="102"/>
-      <c r="D52" s="102" t="s">
+      <c r="C52" s="95"/>
+      <c r="D52" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E52" s="102" t="s">
+      <c r="E52" s="95" t="s">
         <v>401</v>
       </c>
-      <c r="F52" s="102"/>
-      <c r="G52" s="102"/>
-      <c r="H52" s="102"/>
-      <c r="I52" s="102"/>
-      <c r="J52" s="102"/>
-      <c r="K52" s="102"/>
-      <c r="L52" s="102"/>
-      <c r="M52" s="102"/>
-      <c r="N52" s="102"/>
-      <c r="O52" s="102" t="s">
+      <c r="F52" s="95"/>
+      <c r="G52" s="95"/>
+      <c r="H52" s="95"/>
+      <c r="I52" s="95"/>
+      <c r="J52" s="95"/>
+      <c r="K52" s="95"/>
+      <c r="L52" s="95"/>
+      <c r="M52" s="95"/>
+      <c r="N52" s="95"/>
+      <c r="O52" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P52" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
-      <c r="A53" s="102" t="s">
+      <c r="P52" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A53" s="95" t="s">
         <v>145</v>
       </c>
-      <c r="B53" s="102" t="s">
+      <c r="B53" s="95" t="s">
         <v>252</v>
       </c>
-      <c r="C53" s="102"/>
-      <c r="D53" s="102" t="s">
+      <c r="C53" s="95"/>
+      <c r="D53" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E53" s="102" t="s">
+      <c r="E53" s="95" t="s">
         <v>402</v>
       </c>
-      <c r="F53" s="102"/>
-      <c r="G53" s="102"/>
-      <c r="H53" s="102"/>
-      <c r="I53" s="102"/>
-      <c r="J53" s="102"/>
-      <c r="K53" s="102"/>
-      <c r="L53" s="102"/>
-      <c r="M53" s="102"/>
-      <c r="N53" s="102"/>
-      <c r="O53" s="102" t="s">
+      <c r="F53" s="95"/>
+      <c r="G53" s="95"/>
+      <c r="H53" s="95"/>
+      <c r="I53" s="95"/>
+      <c r="J53" s="95"/>
+      <c r="K53" s="95"/>
+      <c r="L53" s="95"/>
+      <c r="M53" s="95"/>
+      <c r="N53" s="95"/>
+      <c r="O53" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P53" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
-      <c r="A54" s="102" t="s">
+      <c r="P53" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A54" s="95" t="s">
         <v>403</v>
       </c>
-      <c r="B54" s="102" t="s">
+      <c r="B54" s="95" t="s">
         <v>244</v>
       </c>
-      <c r="C54" s="102"/>
-      <c r="D54" s="102" t="s">
+      <c r="C54" s="95"/>
+      <c r="D54" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E54" s="102" t="s">
+      <c r="E54" s="95" t="s">
         <v>404</v>
       </c>
-      <c r="F54" s="102"/>
-      <c r="G54" s="102"/>
-      <c r="H54" s="102"/>
-      <c r="I54" s="102"/>
-      <c r="J54" s="102"/>
-      <c r="K54" s="102"/>
-      <c r="L54" s="102"/>
-      <c r="M54" s="102"/>
-      <c r="N54" s="102"/>
-      <c r="O54" s="102" t="s">
+      <c r="F54" s="95"/>
+      <c r="G54" s="95"/>
+      <c r="H54" s="95"/>
+      <c r="I54" s="95"/>
+      <c r="J54" s="95"/>
+      <c r="K54" s="95"/>
+      <c r="L54" s="95"/>
+      <c r="M54" s="95"/>
+      <c r="N54" s="95"/>
+      <c r="O54" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P54" s="108" t="s">
+      <c r="P54" s="96" t="s">
         <v>405</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
-      <c r="A55" s="109" t="s">
+      <c r="A55" s="97" t="s">
         <v>153</v>
       </c>
-      <c r="B55" s="102" t="s">
+      <c r="B55" s="87" t="s">
         <v>248</v>
       </c>
-      <c r="C55" s="102"/>
-      <c r="D55" s="102" t="s">
+      <c r="C55" s="87"/>
+      <c r="D55" s="87" t="s">
         <v>249</v>
       </c>
-      <c r="E55" s="102" t="s">
+      <c r="E55" s="87" t="s">
         <v>406</v>
       </c>
-      <c r="F55" s="102"/>
-      <c r="G55" s="102"/>
-      <c r="H55" s="102"/>
-      <c r="I55" s="102"/>
-      <c r="J55" s="102"/>
-      <c r="K55" s="102"/>
-      <c r="L55" s="102"/>
-      <c r="M55" s="102"/>
-      <c r="N55" s="102"/>
-      <c r="O55" s="102" t="s">
+      <c r="F55" s="87"/>
+      <c r="G55" s="87"/>
+      <c r="H55" s="87"/>
+      <c r="I55" s="87"/>
+      <c r="J55" s="87"/>
+      <c r="K55" s="87"/>
+      <c r="L55" s="87"/>
+      <c r="M55" s="87"/>
+      <c r="N55" s="87"/>
+      <c r="O55" s="87" t="s">
         <v>295</v>
       </c>
-      <c r="P55" s="108" t="s">
+      <c r="P55" s="96" t="s">
         <v>405</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
-      <c r="A56" s="109" t="s">
+      <c r="A56" s="97" t="s">
         <v>407</v>
       </c>
-      <c r="B56" s="102" t="s">
+      <c r="B56" s="87" t="s">
         <v>252</v>
       </c>
-      <c r="C56" s="102"/>
-      <c r="D56" s="102" t="s">
+      <c r="C56" s="87"/>
+      <c r="D56" s="87" t="s">
         <v>249</v>
       </c>
-      <c r="E56" s="102" t="s">
+      <c r="E56" s="87" t="s">
         <v>408</v>
       </c>
-      <c r="F56" s="102" t="s">
+      <c r="F56" s="87" t="s">
         <v>409</v>
       </c>
-      <c r="G56" s="102"/>
-      <c r="H56" s="102"/>
-      <c r="I56" s="102"/>
-      <c r="J56" s="102"/>
-      <c r="K56" s="102"/>
-      <c r="L56" s="102"/>
-      <c r="M56" s="102"/>
-      <c r="N56" s="102"/>
-      <c r="O56" s="102" t="s">
+      <c r="G56" s="87"/>
+      <c r="H56" s="87"/>
+      <c r="I56" s="87"/>
+      <c r="J56" s="87"/>
+      <c r="K56" s="87"/>
+      <c r="L56" s="87"/>
+      <c r="M56" s="87"/>
+      <c r="N56" s="87"/>
+      <c r="O56" s="87" t="s">
         <v>410</v>
       </c>
-      <c r="P56" s="108" t="s">
+      <c r="P56" s="96" t="s">
         <v>405</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
-      <c r="A57" s="109" t="s">
+      <c r="A57" s="97" t="s">
         <v>160</v>
       </c>
-      <c r="B57" s="102" t="s">
+      <c r="B57" s="87" t="s">
         <v>244</v>
       </c>
-      <c r="C57" s="102"/>
-      <c r="D57" s="102" t="s">
+      <c r="C57" s="87"/>
+      <c r="D57" s="87" t="s">
         <v>249</v>
       </c>
-      <c r="E57" s="102" t="s">
+      <c r="E57" s="87" t="s">
         <v>411</v>
       </c>
-      <c r="F57" s="102"/>
-      <c r="G57" s="102"/>
-      <c r="H57" s="102"/>
-      <c r="I57" s="102"/>
-      <c r="J57" s="102"/>
-      <c r="K57" s="102"/>
-      <c r="L57" s="102"/>
-      <c r="M57" s="102"/>
-      <c r="N57" s="102"/>
-      <c r="O57" s="102" t="s">
+      <c r="F57" s="87"/>
+      <c r="G57" s="87"/>
+      <c r="H57" s="87"/>
+      <c r="I57" s="87"/>
+      <c r="J57" s="87"/>
+      <c r="K57" s="87"/>
+      <c r="L57" s="87"/>
+      <c r="M57" s="87"/>
+      <c r="N57" s="87"/>
+      <c r="O57" s="87" t="s">
         <v>410</v>
       </c>
-      <c r="P57" s="108"/>
+      <c r="P57" s="96"/>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
-      <c r="A58" s="109" t="s">
+      <c r="A58" s="97" t="s">
         <v>163</v>
       </c>
-      <c r="B58" s="102" t="s">
+      <c r="B58" s="87" t="s">
         <v>244</v>
       </c>
-      <c r="C58" s="102"/>
-      <c r="D58" s="102" t="s">
+      <c r="C58" s="87"/>
+      <c r="D58" s="87" t="s">
         <v>249</v>
       </c>
-      <c r="E58" s="102" t="s">
+      <c r="E58" s="87" t="s">
         <v>412</v>
       </c>
-      <c r="F58" s="102"/>
-      <c r="G58" s="102"/>
-      <c r="H58" s="102"/>
-      <c r="I58" s="102"/>
-      <c r="J58" s="102"/>
-      <c r="K58" s="102"/>
-      <c r="L58" s="102"/>
-      <c r="M58" s="102"/>
-      <c r="N58" s="102"/>
-      <c r="O58" s="102" t="s">
+      <c r="F58" s="87"/>
+      <c r="G58" s="87"/>
+      <c r="H58" s="87"/>
+      <c r="I58" s="87"/>
+      <c r="J58" s="87"/>
+      <c r="K58" s="87"/>
+      <c r="L58" s="87"/>
+      <c r="M58" s="87"/>
+      <c r="N58" s="87"/>
+      <c r="O58" s="87" t="s">
         <v>410</v>
       </c>
-      <c r="P58" s="108"/>
+      <c r="P58" s="96"/>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
-      <c r="A59" s="109" t="s">
+      <c r="A59" s="97" t="s">
         <v>166</v>
       </c>
-      <c r="B59" s="102" t="s">
+      <c r="B59" s="87" t="s">
         <v>244</v>
       </c>
-      <c r="C59" s="102"/>
-      <c r="D59" s="102" t="s">
+      <c r="C59" s="87"/>
+      <c r="D59" s="87" t="s">
         <v>249</v>
       </c>
-      <c r="E59" s="102" t="s">
+      <c r="E59" s="87" t="s">
         <v>165</v>
       </c>
-      <c r="F59" s="102"/>
-      <c r="G59" s="102"/>
-      <c r="H59" s="102"/>
-      <c r="I59" s="102"/>
-      <c r="J59" s="102"/>
-      <c r="K59" s="102"/>
-      <c r="L59" s="102"/>
-      <c r="M59" s="102"/>
-      <c r="N59" s="102"/>
-      <c r="O59" s="102" t="s">
+      <c r="F59" s="87"/>
+      <c r="G59" s="87"/>
+      <c r="H59" s="87"/>
+      <c r="I59" s="87"/>
+      <c r="J59" s="87"/>
+      <c r="K59" s="87"/>
+      <c r="L59" s="87"/>
+      <c r="M59" s="87"/>
+      <c r="N59" s="87"/>
+      <c r="O59" s="87" t="s">
         <v>410</v>
       </c>
-      <c r="P59" s="110" t="s">
+      <c r="P59" s="98" t="s">
         <v>258</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
-      <c r="A60" s="109" t="s">
+      <c r="A60" s="97" t="s">
         <v>170</v>
       </c>
-      <c r="B60" s="102" t="s">
+      <c r="B60" s="87" t="s">
         <v>260</v>
       </c>
-      <c r="C60" s="102"/>
-      <c r="D60" s="102" t="s">
+      <c r="C60" s="87"/>
+      <c r="D60" s="87" t="s">
         <v>249</v>
       </c>
-      <c r="E60" s="102" t="s">
+      <c r="E60" s="87" t="s">
         <v>413</v>
       </c>
-      <c r="F60" s="102"/>
-      <c r="G60" s="102"/>
-      <c r="H60" s="102"/>
-      <c r="I60" s="102"/>
-      <c r="J60" s="102"/>
-      <c r="K60" s="102"/>
-      <c r="L60" s="102"/>
-      <c r="M60" s="102"/>
-      <c r="N60" s="102"/>
-      <c r="O60" s="102" t="s">
+      <c r="F60" s="87"/>
+      <c r="G60" s="87"/>
+      <c r="H60" s="87"/>
+      <c r="I60" s="87"/>
+      <c r="J60" s="87"/>
+      <c r="K60" s="87"/>
+      <c r="L60" s="87"/>
+      <c r="M60" s="87"/>
+      <c r="N60" s="87"/>
+      <c r="O60" s="87" t="s">
         <v>410</v>
       </c>
-      <c r="P60" s="108"/>
+      <c r="P60" s="96"/>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
-      <c r="A61" s="109" t="s">
+      <c r="A61" s="97" t="s">
         <v>174</v>
       </c>
-      <c r="B61" s="102" t="s">
+      <c r="B61" s="87" t="s">
         <v>263</v>
       </c>
-      <c r="C61" s="102"/>
-      <c r="D61" s="102" t="s">
+      <c r="C61" s="87"/>
+      <c r="D61" s="87" t="s">
         <v>249</v>
       </c>
-      <c r="E61" s="102" t="s">
+      <c r="E61" s="87" t="s">
         <v>414</v>
       </c>
-      <c r="F61" s="102"/>
-      <c r="G61" s="102"/>
-      <c r="H61" s="102"/>
-      <c r="I61" s="102"/>
-      <c r="J61" s="102"/>
-      <c r="K61" s="102"/>
-      <c r="L61" s="102"/>
-      <c r="M61" s="102"/>
-      <c r="N61" s="102"/>
-      <c r="O61" s="102" t="s">
+      <c r="F61" s="87"/>
+      <c r="G61" s="87"/>
+      <c r="H61" s="87"/>
+      <c r="I61" s="87"/>
+      <c r="J61" s="87"/>
+      <c r="K61" s="87"/>
+      <c r="L61" s="87"/>
+      <c r="M61" s="87"/>
+      <c r="N61" s="87"/>
+      <c r="O61" s="87" t="s">
         <v>410</v>
       </c>
-      <c r="P61" s="110" t="s">
+      <c r="P61" s="98" t="s">
         <v>264</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
-      <c r="A62" s="109" t="s">
+      <c r="A62" s="97" t="s">
         <v>178</v>
       </c>
-      <c r="B62" s="102" t="s">
+      <c r="B62" s="87" t="s">
         <v>252</v>
       </c>
-      <c r="C62" s="102"/>
-      <c r="D62" s="102" t="s">
+      <c r="C62" s="87"/>
+      <c r="D62" s="87" t="s">
         <v>249</v>
       </c>
-      <c r="E62" s="102" t="s">
+      <c r="E62" s="87" t="s">
         <v>414</v>
       </c>
-      <c r="F62" s="102"/>
-      <c r="G62" s="102"/>
-      <c r="H62" s="102"/>
-      <c r="I62" s="102"/>
-      <c r="J62" s="102"/>
-      <c r="K62" s="102"/>
-      <c r="L62" s="102"/>
-      <c r="M62" s="102"/>
-      <c r="N62" s="102"/>
-      <c r="O62" s="102" t="s">
+      <c r="F62" s="87"/>
+      <c r="G62" s="87"/>
+      <c r="H62" s="87"/>
+      <c r="I62" s="87"/>
+      <c r="J62" s="87"/>
+      <c r="K62" s="87"/>
+      <c r="L62" s="87"/>
+      <c r="M62" s="87"/>
+      <c r="N62" s="87"/>
+      <c r="O62" s="87" t="s">
         <v>410</v>
       </c>
-      <c r="P62" s="108"/>
+      <c r="P62" s="96"/>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
-      <c r="A63" s="109" t="s">
+      <c r="A63" s="97" t="s">
         <v>183</v>
       </c>
-      <c r="B63" s="102" t="s">
+      <c r="B63" s="87" t="s">
         <v>248</v>
       </c>
-      <c r="C63" s="102"/>
-      <c r="D63" s="102" t="s">
+      <c r="C63" s="87"/>
+      <c r="D63" s="87" t="s">
         <v>249</v>
       </c>
-      <c r="E63" s="102" t="s">
+      <c r="E63" s="87" t="s">
         <v>415</v>
       </c>
-      <c r="F63" s="102"/>
-      <c r="G63" s="102"/>
-      <c r="H63" s="102"/>
-      <c r="I63" s="102"/>
-      <c r="J63" s="102"/>
-      <c r="K63" s="102"/>
-      <c r="L63" s="102"/>
-      <c r="M63" s="102"/>
-      <c r="N63" s="102"/>
-      <c r="O63" s="102" t="s">
+      <c r="F63" s="87"/>
+      <c r="G63" s="87"/>
+      <c r="H63" s="87"/>
+      <c r="I63" s="87"/>
+      <c r="J63" s="87"/>
+      <c r="K63" s="87"/>
+      <c r="L63" s="87"/>
+      <c r="M63" s="87"/>
+      <c r="N63" s="87"/>
+      <c r="O63" s="87" t="s">
         <v>410</v>
       </c>
-      <c r="P63" s="108"/>
+      <c r="P63" s="96"/>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
-      <c r="A64" s="111" t="s">
+      <c r="A64" s="99" t="s">
         <v>187</v>
       </c>
-      <c r="B64" s="102" t="s">
+      <c r="B64" s="87" t="s">
         <v>248</v>
       </c>
-      <c r="C64" s="102"/>
-      <c r="D64" s="102" t="s">
+      <c r="C64" s="87"/>
+      <c r="D64" s="87" t="s">
         <v>249</v>
       </c>
-      <c r="E64" s="102" t="s">
+      <c r="E64" s="87" t="s">
         <v>416</v>
       </c>
-      <c r="F64" s="102"/>
-      <c r="G64" s="102"/>
-      <c r="H64" s="102"/>
-      <c r="I64" s="102"/>
-      <c r="J64" s="102"/>
-      <c r="K64" s="102"/>
-      <c r="L64" s="102"/>
-      <c r="M64" s="102"/>
-      <c r="N64" s="102"/>
-      <c r="O64" s="102" t="s">
+      <c r="F64" s="87"/>
+      <c r="G64" s="87"/>
+      <c r="H64" s="87"/>
+      <c r="I64" s="87"/>
+      <c r="J64" s="87"/>
+      <c r="K64" s="87"/>
+      <c r="L64" s="87"/>
+      <c r="M64" s="87"/>
+      <c r="N64" s="87"/>
+      <c r="O64" s="87" t="s">
         <v>410</v>
       </c>
-      <c r="P64" s="108"/>
+      <c r="P64" s="96"/>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
-      <c r="A65" s="111" t="s">
+      <c r="A65" s="99" t="s">
         <v>417</v>
       </c>
-      <c r="B65" s="102" t="s">
+      <c r="B65" s="87" t="s">
         <v>271</v>
       </c>
-      <c r="C65" s="102"/>
-      <c r="D65" s="102" t="s">
+      <c r="C65" s="87"/>
+      <c r="D65" s="87" t="s">
         <v>249</v>
       </c>
-      <c r="E65" s="102" t="s">
+      <c r="E65" s="87" t="s">
         <v>189</v>
       </c>
-      <c r="F65" s="102"/>
-      <c r="G65" s="102"/>
-      <c r="H65" s="102"/>
-      <c r="I65" s="102"/>
-      <c r="J65" s="102"/>
-      <c r="K65" s="102"/>
-      <c r="L65" s="102"/>
-      <c r="M65" s="102"/>
-      <c r="N65" s="102"/>
-      <c r="O65" s="102" t="s">
+      <c r="F65" s="87"/>
+      <c r="G65" s="87"/>
+      <c r="H65" s="87"/>
+      <c r="I65" s="87"/>
+      <c r="J65" s="87"/>
+      <c r="K65" s="87"/>
+      <c r="L65" s="87"/>
+      <c r="M65" s="87"/>
+      <c r="N65" s="87"/>
+      <c r="O65" s="87" t="s">
         <v>295</v>
       </c>
-      <c r="P65" s="108"/>
+      <c r="P65" s="96"/>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
-      <c r="A66" s="111" t="s">
+      <c r="A66" s="99" t="s">
         <v>418</v>
       </c>
-      <c r="B66" s="102" t="s">
+      <c r="B66" s="87" t="s">
         <v>248</v>
       </c>
-      <c r="C66" s="102"/>
-      <c r="D66" s="102" t="s">
+      <c r="C66" s="87"/>
+      <c r="D66" s="87" t="s">
         <v>249</v>
       </c>
-      <c r="E66" s="102" t="s">
+      <c r="E66" s="87" t="s">
         <v>189</v>
       </c>
-      <c r="F66" s="102" t="s">
+      <c r="F66" s="87" t="s">
         <v>419</v>
       </c>
-      <c r="G66" s="102"/>
-      <c r="H66" s="102"/>
-      <c r="I66" s="102"/>
-      <c r="J66" s="102"/>
-      <c r="K66" s="102"/>
-      <c r="L66" s="102"/>
-      <c r="M66" s="102"/>
-      <c r="N66" s="102"/>
-      <c r="O66" s="102" t="s">
+      <c r="G66" s="87"/>
+      <c r="H66" s="87"/>
+      <c r="I66" s="87"/>
+      <c r="J66" s="87"/>
+      <c r="K66" s="87"/>
+      <c r="L66" s="87"/>
+      <c r="M66" s="87"/>
+      <c r="N66" s="87"/>
+      <c r="O66" s="87" t="s">
         <v>295</v>
       </c>
-      <c r="P66" s="108"/>
+      <c r="P66" s="96"/>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
-      <c r="A67" s="111" t="s">
+      <c r="A67" s="99" t="s">
         <v>198</v>
       </c>
-      <c r="B67" s="102" t="s">
+      <c r="B67" s="87" t="s">
         <v>252</v>
       </c>
-      <c r="C67" s="102"/>
-      <c r="D67" s="102" t="s">
+      <c r="C67" s="87"/>
+      <c r="D67" s="87" t="s">
         <v>249</v>
       </c>
-      <c r="E67" s="102" t="s">
+      <c r="E67" s="87" t="s">
         <v>420</v>
       </c>
-      <c r="F67" s="102"/>
-      <c r="G67" s="102"/>
-      <c r="H67" s="102"/>
-      <c r="I67" s="102"/>
-      <c r="J67" s="102"/>
-      <c r="K67" s="102"/>
-      <c r="L67" s="102"/>
-      <c r="M67" s="102"/>
-      <c r="N67" s="102"/>
-      <c r="O67" s="102" t="s">
+      <c r="F67" s="87"/>
+      <c r="G67" s="87"/>
+      <c r="H67" s="87"/>
+      <c r="I67" s="87"/>
+      <c r="J67" s="87"/>
+      <c r="K67" s="87"/>
+      <c r="L67" s="87"/>
+      <c r="M67" s="87"/>
+      <c r="N67" s="87"/>
+      <c r="O67" s="87" t="s">
         <v>410</v>
       </c>
-      <c r="P67" s="108"/>
+      <c r="P67" s="96"/>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
-      <c r="A68" s="111" t="s">
+      <c r="A68" s="99" t="s">
         <v>202</v>
       </c>
-      <c r="B68" s="102" t="s">
+      <c r="B68" s="87" t="s">
         <v>252</v>
       </c>
-      <c r="C68" s="102"/>
-      <c r="D68" s="102" t="s">
+      <c r="C68" s="87"/>
+      <c r="D68" s="87" t="s">
         <v>249</v>
       </c>
-      <c r="E68" s="102" t="s">
+      <c r="E68" s="87" t="s">
         <v>421</v>
       </c>
-      <c r="F68" s="102"/>
-      <c r="G68" s="102"/>
-      <c r="H68" s="102"/>
-      <c r="I68" s="102"/>
-      <c r="J68" s="102"/>
-      <c r="K68" s="102"/>
-      <c r="L68" s="102"/>
-      <c r="M68" s="102"/>
-      <c r="N68" s="102"/>
-      <c r="O68" s="102" t="s">
+      <c r="F68" s="87"/>
+      <c r="G68" s="87"/>
+      <c r="H68" s="87"/>
+      <c r="I68" s="87"/>
+      <c r="J68" s="87"/>
+      <c r="K68" s="87"/>
+      <c r="L68" s="87"/>
+      <c r="M68" s="87"/>
+      <c r="N68" s="87"/>
+      <c r="O68" s="87" t="s">
         <v>410</v>
       </c>
-      <c r="P68" s="108"/>
+      <c r="P68" s="96"/>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
-      <c r="A69" s="111" t="s">
+      <c r="A69" s="99" t="s">
         <v>205</v>
       </c>
-      <c r="B69" s="102" t="s">
+      <c r="B69" s="87" t="s">
         <v>252</v>
       </c>
-      <c r="C69" s="102"/>
-      <c r="D69" s="102" t="s">
+      <c r="C69" s="87"/>
+      <c r="D69" s="87" t="s">
         <v>249</v>
       </c>
-      <c r="E69" s="102" t="s">
+      <c r="E69" s="87" t="s">
         <v>422</v>
       </c>
-      <c r="F69" s="102"/>
-      <c r="G69" s="102"/>
-      <c r="H69" s="102"/>
-      <c r="I69" s="102"/>
-      <c r="J69" s="102"/>
-      <c r="K69" s="102"/>
-      <c r="L69" s="102"/>
-      <c r="M69" s="102"/>
-      <c r="N69" s="102"/>
-      <c r="O69" s="102" t="s">
+      <c r="F69" s="87"/>
+      <c r="G69" s="87"/>
+      <c r="H69" s="87"/>
+      <c r="I69" s="87"/>
+      <c r="J69" s="87"/>
+      <c r="K69" s="87"/>
+      <c r="L69" s="87"/>
+      <c r="M69" s="87"/>
+      <c r="N69" s="87"/>
+      <c r="O69" s="87" t="s">
         <v>410</v>
       </c>
-      <c r="P69" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
-      <c r="A70" s="102" t="s">
+      <c r="P69" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A70" s="95" t="s">
         <v>423</v>
       </c>
-      <c r="B70" s="102" t="s">
+      <c r="B70" s="95" t="s">
         <v>424</v>
       </c>
-      <c r="C70" s="102"/>
-      <c r="D70" s="102" t="s">
+      <c r="C70" s="95"/>
+      <c r="D70" s="95" t="s">
         <v>298</v>
       </c>
-      <c r="E70" s="102" t="s">
+      <c r="E70" s="95" t="s">
         <v>425</v>
       </c>
-      <c r="F70" s="102"/>
-      <c r="G70" s="102" t="s">
+      <c r="F70" s="95"/>
+      <c r="G70" s="95" t="s">
         <v>426</v>
       </c>
-      <c r="H70" s="102"/>
-      <c r="I70" s="102"/>
-      <c r="J70" s="102"/>
-      <c r="K70" s="102"/>
-      <c r="L70" s="102"/>
-      <c r="M70" s="102"/>
-      <c r="N70" s="102"/>
-      <c r="O70" s="102" t="s">
+      <c r="H70" s="95"/>
+      <c r="I70" s="95"/>
+      <c r="J70" s="95"/>
+      <c r="K70" s="95"/>
+      <c r="L70" s="95"/>
+      <c r="M70" s="95"/>
+      <c r="N70" s="95"/>
+      <c r="O70" s="95" t="s">
         <v>345</v>
       </c>
-      <c r="P70" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
-      <c r="A71" s="102" t="s">
+      <c r="P70" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A71" s="95" t="s">
         <v>427</v>
       </c>
-      <c r="B71" s="102" t="s">
+      <c r="B71" s="95" t="s">
         <v>428</v>
       </c>
-      <c r="C71" s="102"/>
-      <c r="D71" s="102" t="s">
+      <c r="C71" s="95"/>
+      <c r="D71" s="95" t="s">
         <v>298</v>
       </c>
-      <c r="E71" s="102" t="s">
+      <c r="E71" s="95" t="s">
         <v>429</v>
       </c>
-      <c r="F71" s="102"/>
-      <c r="G71" s="102" t="s">
+      <c r="F71" s="95"/>
+      <c r="G71" s="95" t="s">
         <v>430</v>
       </c>
-      <c r="H71" s="102"/>
-      <c r="I71" s="102"/>
-      <c r="J71" s="102"/>
-      <c r="K71" s="102"/>
-      <c r="L71" s="102"/>
-      <c r="M71" s="102"/>
-      <c r="N71" s="102"/>
-      <c r="O71" s="102" t="s">
+      <c r="H71" s="95"/>
+      <c r="I71" s="95"/>
+      <c r="J71" s="95"/>
+      <c r="K71" s="95"/>
+      <c r="L71" s="95"/>
+      <c r="M71" s="95"/>
+      <c r="N71" s="95"/>
+      <c r="O71" s="95" t="s">
         <v>345</v>
       </c>
-      <c r="P71" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
-      <c r="A72" s="102" t="s">
+      <c r="P71" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A72" s="95" t="s">
         <v>431</v>
       </c>
-      <c r="B72" s="102" t="s">
+      <c r="B72" s="95" t="s">
         <v>252</v>
       </c>
-      <c r="C72" s="102"/>
-      <c r="D72" s="102" t="s">
+      <c r="C72" s="95"/>
+      <c r="D72" s="95" t="s">
         <v>249</v>
       </c>
-      <c r="E72" s="102" t="s">
+      <c r="E72" s="95" t="s">
         <v>432</v>
       </c>
-      <c r="F72" s="102"/>
-      <c r="G72" s="102" t="s">
+      <c r="F72" s="95"/>
+      <c r="G72" s="95" t="s">
         <v>433</v>
       </c>
-      <c r="H72" s="102"/>
-      <c r="I72" s="102"/>
-      <c r="J72" s="102"/>
-      <c r="K72" s="102"/>
-      <c r="L72" s="102"/>
-      <c r="M72" s="102"/>
-      <c r="N72" s="102"/>
-      <c r="O72" s="102" t="s">
+      <c r="H72" s="95"/>
+      <c r="I72" s="95"/>
+      <c r="J72" s="95"/>
+      <c r="K72" s="95"/>
+      <c r="L72" s="95"/>
+      <c r="M72" s="95"/>
+      <c r="N72" s="95"/>
+      <c r="O72" s="95" t="s">
         <v>345</v>
       </c>
-      <c r="P72" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
-      <c r="A73" s="102" t="s">
+      <c r="P72" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A73" s="95" t="s">
         <v>434</v>
       </c>
-      <c r="B73" s="102" t="s">
+      <c r="B73" s="95" t="s">
         <v>435</v>
       </c>
-      <c r="C73" s="102"/>
-      <c r="D73" s="102" t="s">
+      <c r="C73" s="95"/>
+      <c r="D73" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E73" s="102" t="s">
+      <c r="E73" s="95" t="s">
         <v>436</v>
       </c>
-      <c r="F73" s="102"/>
-      <c r="G73" s="102" t="s">
+      <c r="F73" s="95"/>
+      <c r="G73" s="95" t="s">
         <v>437</v>
       </c>
-      <c r="H73" s="102"/>
-      <c r="I73" s="102"/>
-      <c r="J73" s="102"/>
-      <c r="K73" s="102"/>
-      <c r="L73" s="102"/>
-      <c r="M73" s="102"/>
-      <c r="N73" s="102"/>
-      <c r="O73" s="102" t="s">
+      <c r="H73" s="95"/>
+      <c r="I73" s="95"/>
+      <c r="J73" s="95"/>
+      <c r="K73" s="95"/>
+      <c r="L73" s="95"/>
+      <c r="M73" s="95"/>
+      <c r="N73" s="95"/>
+      <c r="O73" s="95" t="s">
         <v>345</v>
       </c>
-      <c r="P73" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
-      <c r="A74" s="102" t="s">
+      <c r="P73" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A74" s="95" t="s">
         <v>208</v>
       </c>
-      <c r="B74" s="102" t="s">
+      <c r="B74" s="95" t="s">
         <v>252</v>
       </c>
-      <c r="C74" s="102"/>
-      <c r="D74" s="102" t="s">
+      <c r="C74" s="95"/>
+      <c r="D74" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E74" s="102" t="s">
+      <c r="E74" s="95" t="s">
         <v>438</v>
       </c>
-      <c r="F74" s="102"/>
-      <c r="G74" s="102" t="s">
+      <c r="F74" s="95"/>
+      <c r="G74" s="95" t="s">
         <v>439</v>
       </c>
-      <c r="H74" s="102"/>
-      <c r="I74" s="102"/>
-      <c r="J74" s="102"/>
-      <c r="K74" s="102"/>
-      <c r="L74" s="102"/>
-      <c r="M74" s="102"/>
-      <c r="N74" s="102"/>
-      <c r="O74" s="102" t="s">
+      <c r="H74" s="95"/>
+      <c r="I74" s="95"/>
+      <c r="J74" s="95"/>
+      <c r="K74" s="95"/>
+      <c r="L74" s="95"/>
+      <c r="M74" s="95"/>
+      <c r="N74" s="95"/>
+      <c r="O74" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P74" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
-      <c r="A75" s="102" t="s">
+      <c r="P74" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A75" s="95" t="s">
         <v>440</v>
       </c>
-      <c r="B75" s="102" t="s">
+      <c r="B75" s="95" t="s">
         <v>248</v>
       </c>
-      <c r="C75" s="102" t="s">
+      <c r="C75" s="95" t="s">
         <v>441</v>
       </c>
-      <c r="D75" s="102" t="s">
+      <c r="D75" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="E75" s="102" t="s">
+      <c r="E75" s="95" t="s">
         <v>442</v>
       </c>
-      <c r="F75" s="102"/>
-      <c r="G75" s="102" t="s">
+      <c r="F75" s="95"/>
+      <c r="G75" s="95" t="s">
         <v>443</v>
       </c>
-      <c r="H75" s="102"/>
-      <c r="I75" s="102"/>
-      <c r="J75" s="102"/>
-      <c r="K75" s="102"/>
-      <c r="L75" s="102"/>
-      <c r="M75" s="102"/>
-      <c r="N75" s="102"/>
-      <c r="O75" s="102" t="s">
+      <c r="H75" s="95"/>
+      <c r="I75" s="95"/>
+      <c r="J75" s="95"/>
+      <c r="K75" s="95"/>
+      <c r="L75" s="95"/>
+      <c r="M75" s="95"/>
+      <c r="N75" s="95"/>
+      <c r="O75" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P75" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
-      <c r="A76" s="102" t="s">
+      <c r="P75" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A76" s="95" t="s">
         <v>213</v>
       </c>
-      <c r="B76" s="102" t="s">
+      <c r="B76" s="95" t="s">
         <v>248</v>
       </c>
-      <c r="C76" s="102"/>
-      <c r="D76" s="102" t="s">
+      <c r="C76" s="95"/>
+      <c r="D76" s="95" t="s">
         <v>249</v>
       </c>
-      <c r="E76" s="102" t="s">
+      <c r="E76" s="95" t="s">
         <v>444</v>
       </c>
-      <c r="F76" s="102"/>
-      <c r="G76" s="102" t="s">
+      <c r="F76" s="95"/>
+      <c r="G76" s="95" t="s">
         <v>445</v>
       </c>
-      <c r="H76" s="102"/>
-      <c r="I76" s="102"/>
-      <c r="J76" s="102"/>
-      <c r="K76" s="102"/>
-      <c r="L76" s="102"/>
-      <c r="M76" s="102"/>
-      <c r="N76" s="102"/>
-      <c r="O76" s="102" t="s">
+      <c r="H76" s="95"/>
+      <c r="I76" s="95"/>
+      <c r="J76" s="95"/>
+      <c r="K76" s="95"/>
+      <c r="L76" s="95"/>
+      <c r="M76" s="95"/>
+      <c r="N76" s="95"/>
+      <c r="O76" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P76" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
-      <c r="A77" s="102" t="s">
+      <c r="P76" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A77" s="95" t="s">
         <v>216</v>
       </c>
-      <c r="B77" s="102" t="s">
+      <c r="B77" s="95" t="s">
         <v>248</v>
       </c>
-      <c r="C77" s="102"/>
-      <c r="D77" s="102" t="s">
+      <c r="C77" s="95"/>
+      <c r="D77" s="95" t="s">
         <v>249</v>
       </c>
-      <c r="E77" s="102" t="s">
+      <c r="E77" s="95" t="s">
         <v>446</v>
       </c>
-      <c r="F77" s="102"/>
-      <c r="G77" s="102" t="s">
+      <c r="F77" s="95"/>
+      <c r="G77" s="95" t="s">
         <v>447</v>
       </c>
-      <c r="H77" s="102"/>
-      <c r="I77" s="102"/>
-      <c r="J77" s="102"/>
-      <c r="K77" s="102"/>
-      <c r="L77" s="102"/>
-      <c r="M77" s="102"/>
-      <c r="N77" s="102"/>
-      <c r="O77" s="102" t="s">
+      <c r="H77" s="95"/>
+      <c r="I77" s="95"/>
+      <c r="J77" s="95"/>
+      <c r="K77" s="95"/>
+      <c r="L77" s="95"/>
+      <c r="M77" s="95"/>
+      <c r="N77" s="95"/>
+      <c r="O77" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P77" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
-      <c r="A78" s="102" t="s">
+      <c r="P77" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A78" s="95" t="s">
         <v>223</v>
       </c>
-      <c r="B78" s="102" t="s">
+      <c r="B78" s="95" t="s">
         <v>263</v>
       </c>
-      <c r="C78" s="102"/>
-      <c r="D78" s="102" t="s">
+      <c r="C78" s="95"/>
+      <c r="D78" s="95" t="s">
         <v>249</v>
       </c>
-      <c r="E78" s="102" t="s">
+      <c r="E78" s="95" t="s">
         <v>221</v>
       </c>
-      <c r="F78" s="102"/>
-      <c r="G78" s="102"/>
-      <c r="H78" s="102"/>
-      <c r="I78" s="102"/>
-      <c r="J78" s="102"/>
-      <c r="K78" s="102"/>
-      <c r="L78" s="102"/>
-      <c r="M78" s="102"/>
-      <c r="N78" s="102"/>
-      <c r="O78" s="102" t="s">
+      <c r="F78" s="95"/>
+      <c r="G78" s="95"/>
+      <c r="H78" s="95"/>
+      <c r="I78" s="95"/>
+      <c r="J78" s="95"/>
+      <c r="K78" s="95"/>
+      <c r="L78" s="95"/>
+      <c r="M78" s="95"/>
+      <c r="N78" s="95"/>
+      <c r="O78" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P78" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
-      <c r="A79" s="102" t="s">
+      <c r="P78" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A79" s="95" t="s">
         <v>448</v>
       </c>
-      <c r="B79" s="102" t="s">
+      <c r="B79" s="95" t="s">
         <v>449</v>
       </c>
-      <c r="C79" s="102"/>
-      <c r="D79" s="102" t="s">
+      <c r="C79" s="95"/>
+      <c r="D79" s="95" t="s">
         <v>298</v>
       </c>
-      <c r="E79" s="102" t="s">
+      <c r="E79" s="95" t="s">
         <v>450</v>
       </c>
-      <c r="F79" s="102"/>
-      <c r="G79" s="102" t="s">
+      <c r="F79" s="95"/>
+      <c r="G79" s="95" t="s">
         <v>451</v>
       </c>
-      <c r="H79" s="102"/>
-      <c r="I79" s="102"/>
-      <c r="J79" s="102"/>
-      <c r="K79" s="102"/>
-      <c r="L79" s="102"/>
-      <c r="M79" s="102"/>
-      <c r="N79" s="102"/>
-      <c r="O79" s="102" t="s">
+      <c r="H79" s="95"/>
+      <c r="I79" s="95"/>
+      <c r="J79" s="95"/>
+      <c r="K79" s="95"/>
+      <c r="L79" s="95"/>
+      <c r="M79" s="95"/>
+      <c r="N79" s="95"/>
+      <c r="O79" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P79" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
-      <c r="A80" s="102" t="s">
+      <c r="P79" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A80" s="95" t="s">
         <v>452</v>
       </c>
-      <c r="B80" s="102" t="s">
+      <c r="B80" s="95" t="s">
         <v>252</v>
       </c>
-      <c r="C80" s="102"/>
-      <c r="D80" s="102" t="s">
+      <c r="C80" s="95"/>
+      <c r="D80" s="95" t="s">
         <v>249</v>
       </c>
-      <c r="E80" s="102"/>
-      <c r="F80" s="102"/>
-      <c r="G80" s="102" t="s">
+      <c r="E80" s="95"/>
+      <c r="F80" s="95"/>
+      <c r="G80" s="95" t="s">
         <v>453</v>
       </c>
-      <c r="H80" s="102" t="s">
+      <c r="H80" s="95" t="s">
         <v>454</v>
       </c>
-      <c r="I80" s="102"/>
-      <c r="J80" s="102"/>
-      <c r="K80" s="102"/>
-      <c r="L80" s="102"/>
-      <c r="M80" s="102"/>
-      <c r="N80" s="102"/>
-      <c r="O80" s="102" t="s">
+      <c r="I80" s="95"/>
+      <c r="J80" s="95"/>
+      <c r="K80" s="95"/>
+      <c r="L80" s="95"/>
+      <c r="M80" s="95"/>
+      <c r="N80" s="95"/>
+      <c r="O80" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P80" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
-      <c r="A81" s="102" t="s">
+      <c r="P80" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A81" s="95" t="s">
         <v>455</v>
       </c>
-      <c r="B81" s="102" t="s">
+      <c r="B81" s="95" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="102"/>
-      <c r="D81" s="102" t="s">
+      <c r="C81" s="95"/>
+      <c r="D81" s="95" t="s">
         <v>249</v>
       </c>
-      <c r="E81" s="102"/>
-      <c r="F81" s="102"/>
-      <c r="G81" s="102"/>
-      <c r="H81" s="102" t="s">
+      <c r="E81" s="95"/>
+      <c r="F81" s="95"/>
+      <c r="G81" s="95"/>
+      <c r="H81" s="95" t="s">
         <v>456</v>
       </c>
-      <c r="I81" s="102"/>
-      <c r="J81" s="102"/>
-      <c r="K81" s="102"/>
-      <c r="L81" s="102"/>
-      <c r="M81" s="102"/>
-      <c r="N81" s="102"/>
-      <c r="O81" s="102" t="s">
+      <c r="I81" s="95"/>
+      <c r="J81" s="95"/>
+      <c r="K81" s="95"/>
+      <c r="L81" s="95"/>
+      <c r="M81" s="95"/>
+      <c r="N81" s="95"/>
+      <c r="O81" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P81" s="108"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
-      <c r="A82" s="102" t="s">
+      <c r="P81" s="96"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75" customFormat="1" s="94">
+      <c r="A82" s="95" t="s">
         <v>457</v>
       </c>
-      <c r="B82" s="102" t="s">
+      <c r="B82" s="95" t="s">
         <v>458</v>
       </c>
-      <c r="C82" s="102"/>
-      <c r="D82" s="102" t="s">
+      <c r="C82" s="95"/>
+      <c r="D82" s="95" t="s">
         <v>249</v>
       </c>
-      <c r="E82" s="102"/>
-      <c r="F82" s="102"/>
-      <c r="G82" s="102"/>
-      <c r="H82" s="102"/>
-      <c r="I82" s="102"/>
-      <c r="J82" s="102"/>
-      <c r="K82" s="102"/>
-      <c r="L82" s="102"/>
-      <c r="M82" s="102"/>
-      <c r="N82" s="102" t="s">
+      <c r="E82" s="95"/>
+      <c r="F82" s="95"/>
+      <c r="G82" s="95"/>
+      <c r="H82" s="95"/>
+      <c r="I82" s="95"/>
+      <c r="J82" s="95"/>
+      <c r="K82" s="95"/>
+      <c r="L82" s="95"/>
+      <c r="M82" s="95"/>
+      <c r="N82" s="95" t="s">
         <v>459</v>
       </c>
-      <c r="O82" s="102" t="s">
+      <c r="O82" s="95" t="s">
         <v>295</v>
       </c>
-      <c r="P82" s="108"/>
+      <c r="P82" s="96"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5156,269 +5110,269 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="100" width="37.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="100" width="37.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="100" width="37.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="100" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="93" width="37.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="93" width="37.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="93" width="37.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="93" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="102" t="s">
+      <c r="A1" s="87" t="s">
         <v>239</v>
       </c>
-      <c r="B1" s="102" t="s">
+      <c r="B1" s="87" t="s">
         <v>240</v>
       </c>
-      <c r="C1" s="102" t="s">
+      <c r="C1" s="87" t="s">
         <v>241</v>
       </c>
-      <c r="D1" s="102" t="s">
+      <c r="D1" s="87" t="s">
         <v>242</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="103" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+      <c r="A2" s="88" t="s">
         <v>243</v>
       </c>
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="89" t="s">
         <v>244</v>
       </c>
-      <c r="C2" s="104" t="s">
+      <c r="C2" s="89" t="s">
         <v>245</v>
       </c>
-      <c r="D2" s="102" t="s">
+      <c r="D2" s="87" t="s">
         <v>246</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="103" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+      <c r="A3" s="88" t="s">
         <v>247</v>
       </c>
-      <c r="B3" s="104" t="s">
+      <c r="B3" s="89" t="s">
         <v>248</v>
       </c>
-      <c r="C3" s="104" t="s">
+      <c r="C3" s="89" t="s">
         <v>249</v>
       </c>
-      <c r="D3" s="102" t="s">
+      <c r="D3" s="87" t="s">
         <v>250</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="103" t="s">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+      <c r="A4" s="88" t="s">
         <v>251</v>
       </c>
-      <c r="B4" s="104" t="s">
+      <c r="B4" s="89" t="s">
         <v>252</v>
       </c>
-      <c r="C4" s="104" t="s">
+      <c r="C4" s="89" t="s">
         <v>249</v>
       </c>
-      <c r="D4" s="102" t="s">
+      <c r="D4" s="87" t="s">
         <v>253</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="105" t="s">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+      <c r="A5" s="90" t="s">
         <v>254</v>
       </c>
-      <c r="B5" s="104" t="s">
+      <c r="B5" s="89" t="s">
         <v>244</v>
       </c>
-      <c r="C5" s="104" t="s">
+      <c r="C5" s="89" t="s">
         <v>249</v>
       </c>
-      <c r="D5" s="102" t="s">
+      <c r="D5" s="87" t="s">
         <v>255</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="105" t="s">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+      <c r="A6" s="90" t="s">
         <v>256</v>
       </c>
-      <c r="B6" s="104" t="s">
+      <c r="B6" s="89" t="s">
         <v>244</v>
       </c>
-      <c r="C6" s="104" t="s">
+      <c r="C6" s="89" t="s">
         <v>249</v>
       </c>
-      <c r="D6" s="102" t="s">
+      <c r="D6" s="87" t="s">
         <v>255</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="103" t="s">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="20.25">
+      <c r="A7" s="88" t="s">
         <v>257</v>
       </c>
-      <c r="B7" s="104" t="s">
+      <c r="B7" s="89" t="s">
         <v>244</v>
       </c>
-      <c r="C7" s="104" t="s">
+      <c r="C7" s="89" t="s">
         <v>249</v>
       </c>
-      <c r="D7" s="106" t="s">
+      <c r="D7" s="91" t="s">
         <v>258</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="103" t="s">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+      <c r="A8" s="88" t="s">
         <v>259</v>
       </c>
-      <c r="B8" s="104" t="s">
+      <c r="B8" s="89" t="s">
         <v>260</v>
       </c>
-      <c r="C8" s="104" t="s">
+      <c r="C8" s="89" t="s">
         <v>249</v>
       </c>
-      <c r="D8" s="102" t="s">
+      <c r="D8" s="87" t="s">
         <v>261</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="107" t="s">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="47.25">
+      <c r="A9" s="92" t="s">
         <v>262</v>
       </c>
-      <c r="B9" s="104" t="s">
+      <c r="B9" s="89" t="s">
         <v>263</v>
       </c>
-      <c r="C9" s="104" t="s">
+      <c r="C9" s="89" t="s">
         <v>249</v>
       </c>
-      <c r="D9" s="106" t="s">
+      <c r="D9" s="91" t="s">
         <v>264</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="103" t="s">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+      <c r="A10" s="88" t="s">
         <v>265</v>
       </c>
-      <c r="B10" s="104" t="s">
+      <c r="B10" s="89" t="s">
         <v>252</v>
       </c>
-      <c r="C10" s="104" t="s">
+      <c r="C10" s="89" t="s">
         <v>249</v>
       </c>
-      <c r="D10" s="102" t="s">
+      <c r="D10" s="87" t="s">
         <v>266</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="105" t="s">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+      <c r="A11" s="90" t="s">
         <v>267</v>
       </c>
-      <c r="B11" s="104" t="s">
+      <c r="B11" s="89" t="s">
         <v>248</v>
       </c>
-      <c r="C11" s="104" t="s">
+      <c r="C11" s="89" t="s">
         <v>249</v>
       </c>
-      <c r="D11" s="102" t="s">
+      <c r="D11" s="87" t="s">
         <v>268</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="105" t="s">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
+      <c r="A12" s="90" t="s">
         <v>269</v>
       </c>
-      <c r="B12" s="104" t="s">
+      <c r="B12" s="89" t="s">
         <v>248</v>
       </c>
-      <c r="C12" s="104" t="s">
+      <c r="C12" s="89" t="s">
         <v>249</v>
       </c>
-      <c r="D12" s="102" t="s">
+      <c r="D12" s="87" t="s">
         <v>268</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="107" t="s">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
+      <c r="A13" s="92" t="s">
         <v>270</v>
       </c>
-      <c r="B13" s="104" t="s">
+      <c r="B13" s="89" t="s">
         <v>271</v>
       </c>
-      <c r="C13" s="104" t="s">
+      <c r="C13" s="89" t="s">
         <v>249</v>
       </c>
-      <c r="D13" s="102" t="s">
+      <c r="D13" s="87" t="s">
         <v>272</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="107" t="s">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
+      <c r="A14" s="92" t="s">
         <v>273</v>
       </c>
-      <c r="B14" s="104" t="s">
+      <c r="B14" s="89" t="s">
         <v>248</v>
       </c>
-      <c r="C14" s="104" t="s">
+      <c r="C14" s="89" t="s">
         <v>249</v>
       </c>
-      <c r="D14" s="102"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="105" t="s">
+      <c r="D14" s="87"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
+      <c r="A15" s="90" t="s">
         <v>274</v>
       </c>
-      <c r="B15" s="104" t="s">
+      <c r="B15" s="89" t="s">
         <v>252</v>
       </c>
-      <c r="C15" s="104" t="s">
+      <c r="C15" s="89" t="s">
         <v>249</v>
       </c>
-      <c r="D15" s="102" t="s">
+      <c r="D15" s="87" t="s">
         <v>253</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="105" t="s">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
+      <c r="A16" s="90" t="s">
         <v>275</v>
       </c>
-      <c r="B16" s="104" t="s">
+      <c r="B16" s="89" t="s">
         <v>252</v>
       </c>
-      <c r="C16" s="104" t="s">
+      <c r="C16" s="89" t="s">
         <v>249</v>
       </c>
-      <c r="D16" s="102" t="s">
+      <c r="D16" s="87" t="s">
         <v>253</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="107" t="s">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="20.25">
+      <c r="A17" s="92" t="s">
         <v>276</v>
       </c>
-      <c r="B17" s="104" t="s">
+      <c r="B17" s="89" t="s">
         <v>252</v>
       </c>
-      <c r="C17" s="104" t="s">
+      <c r="C17" s="89" t="s">
         <v>249</v>
       </c>
-      <c r="D17" s="102" t="s">
+      <c r="D17" s="87" t="s">
         <v>277</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="102"/>
-      <c r="B18" s="102"/>
-      <c r="C18" s="102"/>
-      <c r="D18" s="102"/>
+      <c r="A18" s="87"/>
+      <c r="B18" s="87"/>
+      <c r="C18" s="87"/>
+      <c r="D18" s="87"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="102"/>
-      <c r="B19" s="102"/>
-      <c r="C19" s="102"/>
-      <c r="D19" s="102"/>
+      <c r="A19" s="87"/>
+      <c r="B19" s="87"/>
+      <c r="C19" s="87"/>
+      <c r="D19" s="87"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="102" t="s">
+      <c r="A20" s="87" t="s">
         <v>278</v>
       </c>
-      <c r="B20" s="102" t="s">
+      <c r="B20" s="87" t="s">
         <v>279</v>
       </c>
-      <c r="C20" s="102"/>
-      <c r="D20" s="102"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="87"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5433,15 +5387,15 @@
   <dimension ref="A1:I65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="100" width="21.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="100" width="30.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="100" width="15.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="100" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="100" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="100" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="101" width="59.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="101" width="29.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="100" width="19.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="85" width="21.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="85" width="30.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="85" width="15.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="85" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="85" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="85" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="86" width="59.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="86" width="29.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="85" width="19.719285714285714" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -5612,7 +5566,7 @@
       <c r="E9" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="27" t="s">
+      <c r="F9" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G9" s="23" t="s">
@@ -5632,7 +5586,7 @@
       <c r="B10" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="26" t="s">
         <v>23</v>
       </c>
       <c r="D10" s="26" t="s">
@@ -5644,7 +5598,7 @@
       <c r="F10" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="28" t="s">
+      <c r="G10" s="27" t="s">
         <v>17</v>
       </c>
       <c r="H10" s="14" t="s">
@@ -5661,7 +5615,7 @@
       <c r="B11" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="26" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="26" t="s">
@@ -5673,7 +5627,7 @@
       <c r="F11" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="29" t="s">
+      <c r="G11" s="28" t="s">
         <v>30</v>
       </c>
       <c r="H11" s="24" t="s">
@@ -5690,7 +5644,7 @@
       <c r="B12" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="C12" s="26" t="s">
         <v>33</v>
       </c>
       <c r="D12" s="26" t="s">
@@ -5702,7 +5656,7 @@
       <c r="F12" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="28" t="s">
+      <c r="G12" s="27" t="s">
         <v>17</v>
       </c>
       <c r="H12" s="14" t="s">
@@ -5719,7 +5673,7 @@
       <c r="B13" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="27" t="s">
+      <c r="C13" s="26" t="s">
         <v>37</v>
       </c>
       <c r="D13" s="26" t="s">
@@ -5748,7 +5702,7 @@
       <c r="B14" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="27" t="s">
+      <c r="C14" s="26" t="s">
         <v>41</v>
       </c>
       <c r="D14" s="26" t="s">
@@ -5777,7 +5731,7 @@
       <c r="B15" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C15" s="26" t="s">
         <v>41</v>
       </c>
       <c r="D15" s="26" t="s">
@@ -5806,7 +5760,7 @@
       <c r="B16" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="27" t="s">
+      <c r="C16" s="26" t="s">
         <v>49</v>
       </c>
       <c r="D16" s="26" t="s">
@@ -5835,7 +5789,7 @@
       <c r="B17" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="26" t="s">
         <v>53</v>
       </c>
       <c r="D17" s="26" t="s">
@@ -5858,45 +5812,45 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="66.75">
-      <c r="A18" s="30" t="s">
+      <c r="A18" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="31" t="s">
+      <c r="B18" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="32" t="s">
+      <c r="C18" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="E18" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="F18" s="31" t="s">
+      <c r="F18" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="G18" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="H18" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="I18" s="34" t="s">
+      <c r="G18" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18" s="32" t="s">
         <v>17</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="66.75">
-      <c r="A19" s="35" t="s">
+      <c r="A19" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="B19" s="36" t="s">
+      <c r="B19" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="C19" s="27" t="s">
+      <c r="C19" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="37" t="s">
+      <c r="D19" s="35" t="s">
         <v>60</v>
       </c>
       <c r="E19" s="26" t="s">
@@ -5916,22 +5870,22 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="66.75">
-      <c r="A20" s="38" t="s">
+      <c r="A20" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="B20" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" s="41" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="F20" s="39" t="s">
+      <c r="B20" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="37" t="s">
         <v>17</v>
       </c>
       <c r="G20" s="14" t="s">
@@ -5945,22 +5899,22 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="42" t="s">
+      <c r="A21" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="B21" s="43" t="s">
+      <c r="B21" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="43" t="s">
+      <c r="C21" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="44" t="s">
+      <c r="D21" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="44" t="s">
+      <c r="E21" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="F21" s="44" t="s">
+      <c r="F21" s="40" t="s">
         <v>15</v>
       </c>
       <c r="G21" s="14" t="s">
@@ -5974,9 +5928,9 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="66.75">
-      <c r="A22" s="45"/>
-      <c r="B22" s="46"/>
-      <c r="C22" s="46"/>
+      <c r="A22" s="41"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="17"/>
@@ -5991,12 +5945,12 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
-      <c r="A23" s="47"/>
-      <c r="B23" s="48"/>
-      <c r="C23" s="48"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
+      <c r="A23" s="42"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
       <c r="G23" s="14" t="s">
         <v>74</v>
       </c>
@@ -6008,16 +5962,16 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="66.75">
-      <c r="A24" s="42" t="s">
+      <c r="A24" s="39" t="s">
         <v>76</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C24" s="50" t="s">
+      <c r="C24" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="51" t="s">
+      <c r="D24" s="44" t="s">
         <v>60</v>
       </c>
       <c r="E24" s="12" t="s">
@@ -6037,16 +5991,16 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="66.75">
-      <c r="A25" s="47"/>
-      <c r="B25" s="49"/>
-      <c r="C25" s="48"/>
-      <c r="D25" s="52"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="53" t="s">
+      <c r="A25" s="42"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="H25" s="53" t="s">
+      <c r="H25" s="14" t="s">
         <v>81</v>
       </c>
       <c r="I25" s="19" t="s">
@@ -6054,16 +6008,16 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="66.75">
-      <c r="A26" s="54" t="s">
+      <c r="A26" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="B26" s="27" t="s">
+      <c r="B26" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="C26" s="27" t="s">
+      <c r="C26" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="27" t="s">
+      <c r="D26" s="26" t="s">
         <v>68</v>
       </c>
       <c r="E26" s="26" t="s">
@@ -6075,24 +6029,24 @@
       <c r="G26" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="H26" s="55" t="s">
+      <c r="H26" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="I26" s="56" t="s">
+      <c r="I26" s="48" t="s">
         <v>17</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="66.75">
-      <c r="A27" s="54" t="s">
+      <c r="A27" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="B27" s="27" t="s">
+      <c r="B27" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="C27" s="27" t="s">
+      <c r="C27" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="57" t="s">
+      <c r="D27" s="49" t="s">
         <v>60</v>
       </c>
       <c r="E27" s="26" t="s">
@@ -6104,7 +6058,7 @@
       <c r="G27" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="H27" s="28" t="s">
+      <c r="H27" s="27" t="s">
         <v>89</v>
       </c>
       <c r="I27" s="19" t="s">
@@ -6112,16 +6066,16 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="66.75">
-      <c r="A28" s="54" t="s">
+      <c r="A28" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="B28" s="27" t="s">
+      <c r="B28" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="C28" s="27" t="s">
+      <c r="C28" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="D28" s="57" t="s">
+      <c r="D28" s="49" t="s">
         <v>60</v>
       </c>
       <c r="E28" s="26" t="s">
@@ -6133,24 +6087,24 @@
       <c r="G28" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="H28" s="55" t="s">
+      <c r="H28" s="47" t="s">
         <v>93</v>
       </c>
-      <c r="I28" s="56" t="s">
+      <c r="I28" s="48" t="s">
         <v>17</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="66.75">
-      <c r="A29" s="54" t="s">
+      <c r="A29" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="B29" s="27" t="s">
+      <c r="B29" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="C29" s="40" t="s">
+      <c r="C29" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="D29" s="58" t="s">
+      <c r="D29" s="50" t="s">
         <v>60</v>
       </c>
       <c r="E29" s="26" t="s">
@@ -6162,7 +6116,7 @@
       <c r="G29" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="H29" s="28" t="s">
+      <c r="H29" s="27" t="s">
         <v>97</v>
       </c>
       <c r="I29" s="19" t="s">
@@ -6176,10 +6130,10 @@
       <c r="B30" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="C30" s="59" t="s">
+      <c r="C30" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="D30" s="60" t="s">
+      <c r="D30" s="51" t="s">
         <v>60</v>
       </c>
       <c r="E30" s="26" t="s">
@@ -6188,7 +6142,7 @@
       <c r="F30" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G30" s="61" t="s">
+      <c r="G30" s="52" t="s">
         <v>17</v>
       </c>
       <c r="H30" s="14" t="s">
@@ -6199,28 +6153,28 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="66.75">
-      <c r="A31" s="62" t="s">
+      <c r="A31" s="53" t="s">
         <v>101</v>
       </c>
       <c r="B31" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="C31" s="63" t="s">
+      <c r="C31" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="D31" s="57" t="s">
+      <c r="D31" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="E31" s="27" t="s">
+      <c r="E31" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="F31" s="27" t="s">
+      <c r="F31" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G31" s="64" t="s">
+      <c r="G31" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="H31" s="65" t="s">
+      <c r="H31" s="56" t="s">
         <v>105</v>
       </c>
       <c r="I31" s="19" t="s">
@@ -6228,28 +6182,28 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="66.75">
-      <c r="A32" s="66" t="s">
+      <c r="A32" s="57" t="s">
         <v>106</v>
       </c>
       <c r="B32" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="C32" s="63" t="s">
+      <c r="C32" s="54" t="s">
         <v>108</v>
       </c>
-      <c r="D32" s="57" t="s">
+      <c r="D32" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="E32" s="27" t="s">
+      <c r="E32" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="F32" s="27" t="s">
+      <c r="F32" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G32" s="67" t="s">
+      <c r="G32" s="58" t="s">
         <v>109</v>
       </c>
-      <c r="H32" s="68" t="s">
+      <c r="H32" s="59" t="s">
         <v>89</v>
       </c>
       <c r="I32" s="19" t="s">
@@ -6257,16 +6211,16 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="66.75">
-      <c r="A33" s="54" t="s">
+      <c r="A33" s="46" t="s">
         <v>110</v>
       </c>
-      <c r="B33" s="69" t="s">
+      <c r="B33" s="60" t="s">
         <v>111</v>
       </c>
-      <c r="C33" s="49" t="s">
+      <c r="C33" s="43" t="s">
         <v>112</v>
       </c>
-      <c r="D33" s="70" t="s">
+      <c r="D33" s="61" t="s">
         <v>113</v>
       </c>
       <c r="E33" s="26" t="s">
@@ -6275,27 +6229,27 @@
       <c r="F33" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G33" s="71" t="s">
+      <c r="G33" s="62" t="s">
         <v>114</v>
       </c>
       <c r="H33" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="I33" s="72" t="s">
+      <c r="I33" s="63" t="s">
         <v>116</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="66.75">
-      <c r="A34" s="54" t="s">
+      <c r="A34" s="46" t="s">
         <v>117</v>
       </c>
       <c r="B34" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="C34" s="27" t="s">
+      <c r="C34" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="D34" s="57" t="s">
+      <c r="D34" s="49" t="s">
         <v>60</v>
       </c>
       <c r="E34" s="26" t="s">
@@ -6310,21 +6264,21 @@
       <c r="H34" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="I34" s="72" t="s">
+      <c r="I34" s="63" t="s">
         <v>116</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="66.75">
-      <c r="A35" s="54" t="s">
+      <c r="A35" s="46" t="s">
         <v>121</v>
       </c>
       <c r="B35" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="C35" s="27" t="s">
+      <c r="C35" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="D35" s="57" t="s">
+      <c r="D35" s="49" t="s">
         <v>60</v>
       </c>
       <c r="E35" s="26" t="s">
@@ -6339,21 +6293,21 @@
       <c r="H35" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="I35" s="72" t="s">
+      <c r="I35" s="63" t="s">
         <v>125</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="66.75">
-      <c r="A36" s="54" t="s">
+      <c r="A36" s="46" t="s">
         <v>126</v>
       </c>
       <c r="B36" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="C36" s="27" t="s">
+      <c r="C36" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="D36" s="57" t="s">
+      <c r="D36" s="49" t="s">
         <v>60</v>
       </c>
       <c r="E36" s="26" t="s">
@@ -6373,16 +6327,16 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="66.75">
-      <c r="A37" s="54" t="s">
+      <c r="A37" s="46" t="s">
         <v>129</v>
       </c>
       <c r="B37" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="C37" s="27" t="s">
+      <c r="C37" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="D37" s="57" t="s">
+      <c r="D37" s="49" t="s">
         <v>60</v>
       </c>
       <c r="E37" s="26" t="s">
@@ -6394,7 +6348,7 @@
       <c r="G37" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="H37" s="65" t="s">
+      <c r="H37" s="56" t="s">
         <v>132</v>
       </c>
       <c r="I37" s="19" t="s">
@@ -6402,16 +6356,16 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="66.75">
-      <c r="A38" s="54" t="s">
+      <c r="A38" s="46" t="s">
         <v>133</v>
       </c>
       <c r="B38" s="26" t="s">
         <v>134</v>
       </c>
-      <c r="C38" s="27" t="s">
+      <c r="C38" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="D38" s="57" t="s">
+      <c r="D38" s="49" t="s">
         <v>60</v>
       </c>
       <c r="E38" s="26" t="s">
@@ -6424,21 +6378,21 @@
         <v>135</v>
       </c>
       <c r="H38" s="3"/>
-      <c r="I38" s="56" t="s">
+      <c r="I38" s="48" t="s">
         <v>17</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="66.75">
-      <c r="A39" s="54" t="s">
+      <c r="A39" s="46" t="s">
         <v>136</v>
       </c>
       <c r="B39" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="C39" s="27" t="s">
+      <c r="C39" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="D39" s="57" t="s">
+      <c r="D39" s="49" t="s">
         <v>60</v>
       </c>
       <c r="E39" s="26" t="s">
@@ -6450,7 +6404,7 @@
       <c r="G39" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="H39" s="28" t="s">
+      <c r="H39" s="27" t="s">
         <v>132</v>
       </c>
       <c r="I39" s="19" t="s">
@@ -6458,19 +6412,19 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="66.75">
-      <c r="A40" s="47" t="s">
+      <c r="A40" s="42" t="s">
         <v>139</v>
       </c>
-      <c r="B40" s="27" t="s">
+      <c r="B40" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="C40" s="27" t="s">
+      <c r="C40" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="57" t="s">
+      <c r="D40" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="E40" s="27" t="s">
+      <c r="E40" s="26" t="s">
         <v>50</v>
       </c>
       <c r="F40" s="26" t="s">
@@ -6487,22 +6441,22 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="66.75">
-      <c r="A41" s="47" t="s">
+      <c r="A41" s="42" t="s">
         <v>142</v>
       </c>
-      <c r="B41" s="27" t="s">
+      <c r="B41" s="26" t="s">
         <v>143</v>
       </c>
-      <c r="C41" s="27" t="s">
+      <c r="C41" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="D41" s="57" t="s">
+      <c r="D41" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="E41" s="27" t="s">
+      <c r="E41" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="F41" s="73" t="s">
+      <c r="F41" s="64" t="s">
         <v>144</v>
       </c>
       <c r="G41" s="24" t="s">
@@ -6516,19 +6470,19 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="66.75">
-      <c r="A42" s="74" t="s">
+      <c r="A42" s="65" t="s">
         <v>146</v>
       </c>
-      <c r="B42" s="27" t="s">
+      <c r="B42" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="C42" s="75" t="s">
+      <c r="C42" s="25" t="s">
         <v>148</v>
       </c>
-      <c r="D42" s="57" t="s">
+      <c r="D42" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="E42" s="76" t="s">
+      <c r="E42" s="64" t="s">
         <v>14</v>
       </c>
       <c r="F42" s="26" t="s">
@@ -6545,22 +6499,22 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
-      <c r="A43" s="77" t="s">
+      <c r="A43" s="66" t="s">
         <v>150</v>
       </c>
-      <c r="B43" s="48" t="s">
+      <c r="B43" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="C43" s="40" t="s">
+      <c r="C43" s="37" t="s">
         <v>152</v>
       </c>
-      <c r="D43" s="58" t="s">
+      <c r="D43" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="E43" s="40" t="s">
+      <c r="E43" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="F43" s="78" t="s">
+      <c r="F43" s="67" t="s">
         <v>15</v>
       </c>
       <c r="G43" s="24" t="s">
@@ -6574,28 +6528,28 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
-      <c r="A44" s="79" t="s">
+      <c r="A44" s="42" t="s">
         <v>154</v>
       </c>
-      <c r="B44" s="27" t="s">
+      <c r="B44" s="26" t="s">
         <v>155</v>
       </c>
-      <c r="C44" s="80" t="s">
-        <v>17</v>
-      </c>
-      <c r="D44" s="81" t="s">
+      <c r="C44" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="E44" s="82" t="s">
+      <c r="E44" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="F44" s="83" t="s">
+      <c r="F44" s="71" t="s">
         <v>15</v>
       </c>
       <c r="G44" s="24" t="s">
         <v>156</v>
       </c>
-      <c r="H44" s="84" t="s">
+      <c r="H44" s="72" t="s">
         <v>17</v>
       </c>
       <c r="I44" s="19" t="s">
@@ -6603,22 +6557,22 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
-      <c r="A45" s="77" t="s">
+      <c r="A45" s="66" t="s">
         <v>157</v>
       </c>
-      <c r="B45" s="46" t="s">
+      <c r="B45" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="C45" s="76" t="s">
+      <c r="C45" s="64" t="s">
         <v>159</v>
       </c>
-      <c r="D45" s="60" t="s">
+      <c r="D45" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="E45" s="59" t="s">
+      <c r="E45" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="F45" s="85" t="s">
+      <c r="F45" s="73" t="s">
         <v>15</v>
       </c>
       <c r="G45" s="24" t="s">
@@ -6632,22 +6586,22 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
-      <c r="A46" s="77" t="s">
+      <c r="A46" s="66" t="s">
         <v>161</v>
       </c>
-      <c r="B46" s="86" t="s">
+      <c r="B46" s="74" t="s">
         <v>162</v>
       </c>
-      <c r="C46" s="76" t="s">
+      <c r="C46" s="64" t="s">
         <v>159</v>
       </c>
-      <c r="D46" s="57" t="s">
+      <c r="D46" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="E46" s="27" t="s">
+      <c r="E46" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="F46" s="87" t="s">
+      <c r="F46" s="60" t="s">
         <v>15</v>
       </c>
       <c r="G46" s="24" t="s">
@@ -6661,22 +6615,22 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
-      <c r="A47" s="77" t="s">
+      <c r="A47" s="66" t="s">
         <v>164</v>
       </c>
-      <c r="B47" s="48" t="s">
+      <c r="B47" s="43" t="s">
         <v>165</v>
       </c>
-      <c r="C47" s="76" t="s">
+      <c r="C47" s="64" t="s">
         <v>159</v>
       </c>
-      <c r="D47" s="57" t="s">
+      <c r="D47" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="E47" s="27" t="s">
+      <c r="E47" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="F47" s="87" t="s">
+      <c r="F47" s="60" t="s">
         <v>15</v>
       </c>
       <c r="G47" s="24" t="s">
@@ -6690,22 +6644,22 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="66.75">
-      <c r="A48" s="77" t="s">
+      <c r="A48" s="66" t="s">
         <v>167</v>
       </c>
-      <c r="B48" s="48" t="s">
+      <c r="B48" s="43" t="s">
         <v>168</v>
       </c>
-      <c r="C48" s="88" t="s">
+      <c r="C48" s="75" t="s">
         <v>169</v>
       </c>
-      <c r="D48" s="57" t="s">
+      <c r="D48" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="E48" s="27" t="s">
+      <c r="E48" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="F48" s="87" t="s">
+      <c r="F48" s="60" t="s">
         <v>15</v>
       </c>
       <c r="G48" s="24" t="s">
@@ -6719,22 +6673,22 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
-      <c r="A49" s="89" t="s">
+      <c r="A49" s="76" t="s">
         <v>171</v>
       </c>
-      <c r="B49" s="48" t="s">
+      <c r="B49" s="43" t="s">
         <v>172</v>
       </c>
-      <c r="C49" s="82" t="s">
+      <c r="C49" s="70" t="s">
         <v>173</v>
       </c>
-      <c r="D49" s="58" t="s">
+      <c r="D49" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="E49" s="40" t="s">
+      <c r="E49" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="F49" s="90" t="s">
+      <c r="F49" s="67" t="s">
         <v>144</v>
       </c>
       <c r="G49" s="24" t="s">
@@ -6748,22 +6702,22 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="117.75">
-      <c r="A50" s="91" t="s">
+      <c r="A50" s="77" t="s">
         <v>175</v>
       </c>
-      <c r="B50" s="27" t="s">
+      <c r="B50" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="C50" s="59" t="s">
+      <c r="C50" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="D50" s="81" t="s">
+      <c r="D50" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="E50" s="82" t="s">
+      <c r="E50" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="F50" s="83" t="s">
+      <c r="F50" s="71" t="s">
         <v>15</v>
       </c>
       <c r="G50" s="24" t="s">
@@ -6777,22 +6731,22 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="123.75">
-      <c r="A51" s="79" t="s">
+      <c r="A51" s="42" t="s">
         <v>179</v>
       </c>
-      <c r="B51" s="27" t="s">
+      <c r="B51" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="C51" s="27" t="s">
+      <c r="C51" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="D51" s="81" t="s">
+      <c r="D51" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="E51" s="82" t="s">
+      <c r="E51" s="70" t="s">
         <v>182</v>
       </c>
-      <c r="F51" s="83" t="s">
+      <c r="F51" s="71" t="s">
         <v>144</v>
       </c>
       <c r="G51" s="24" t="s">
@@ -6806,22 +6760,22 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="66.75">
-      <c r="A52" s="79" t="s">
+      <c r="A52" s="42" t="s">
         <v>184</v>
       </c>
-      <c r="B52" s="27" t="s">
+      <c r="B52" s="26" t="s">
         <v>185</v>
       </c>
-      <c r="C52" s="27" t="s">
+      <c r="C52" s="26" t="s">
         <v>186</v>
       </c>
-      <c r="D52" s="81" t="s">
+      <c r="D52" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="E52" s="82" t="s">
+      <c r="E52" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="F52" s="83" t="s">
+      <c r="F52" s="71" t="s">
         <v>15</v>
       </c>
       <c r="G52" s="24" t="s">
@@ -6835,22 +6789,22 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="66.75">
-      <c r="A53" s="79" t="s">
+      <c r="A53" s="42" t="s">
         <v>188</v>
       </c>
-      <c r="B53" s="27" t="s">
+      <c r="B53" s="26" t="s">
         <v>189</v>
       </c>
-      <c r="C53" s="27" t="s">
+      <c r="C53" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="D53" s="81" t="s">
+      <c r="D53" s="69" t="s">
         <v>60</v>
       </c>
       <c r="E53" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="F53" s="83" t="s">
+      <c r="F53" s="71" t="s">
         <v>15</v>
       </c>
       <c r="G53" s="24" t="s">
@@ -6864,28 +6818,28 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="66.75">
-      <c r="A54" s="79" t="s">
+      <c r="A54" s="42" t="s">
         <v>192</v>
       </c>
-      <c r="B54" s="92" t="s">
+      <c r="B54" s="78" t="s">
         <v>189</v>
       </c>
-      <c r="C54" s="92" t="s">
+      <c r="C54" s="78" t="s">
         <v>193</v>
       </c>
-      <c r="D54" s="93" t="s">
+      <c r="D54" s="79" t="s">
         <v>60</v>
       </c>
-      <c r="E54" s="94" t="s">
+      <c r="E54" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="F54" s="95" t="s">
+      <c r="F54" s="80" t="s">
         <v>15</v>
       </c>
       <c r="G54" s="24" t="s">
         <v>194</v>
       </c>
-      <c r="H54" s="84" t="s">
+      <c r="H54" s="72" t="s">
         <v>195</v>
       </c>
       <c r="I54" s="19" t="s">
@@ -6893,22 +6847,22 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
-      <c r="A55" s="79" t="s">
+      <c r="A55" s="42" t="s">
         <v>196</v>
       </c>
-      <c r="B55" s="27" t="s">
+      <c r="B55" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="C55" s="96" t="s">
-        <v>17</v>
-      </c>
-      <c r="D55" s="81" t="s">
+      <c r="C55" s="81" t="s">
+        <v>17</v>
+      </c>
+      <c r="D55" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="E55" s="76" t="s">
+      <c r="E55" s="64" t="s">
         <v>182</v>
       </c>
-      <c r="F55" s="83" t="s">
+      <c r="F55" s="71" t="s">
         <v>15</v>
       </c>
       <c r="G55" s="24" t="s">
@@ -6922,22 +6876,22 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="66.75">
-      <c r="A56" s="79" t="s">
+      <c r="A56" s="42" t="s">
         <v>199</v>
       </c>
-      <c r="B56" s="27" t="s">
+      <c r="B56" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="C56" s="27" t="s">
+      <c r="C56" s="26" t="s">
         <v>201</v>
       </c>
-      <c r="D56" s="81" t="s">
+      <c r="D56" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="E56" s="27" t="s">
+      <c r="E56" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="F56" s="83" t="s">
+      <c r="F56" s="71" t="s">
         <v>15</v>
       </c>
       <c r="G56" s="24" t="s">
@@ -6951,22 +6905,22 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="66.75">
-      <c r="A57" s="79" t="s">
+      <c r="A57" s="42" t="s">
         <v>203</v>
       </c>
-      <c r="B57" s="27" t="s">
+      <c r="B57" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="C57" s="63" t="s">
-        <v>17</v>
-      </c>
-      <c r="D57" s="81" t="s">
+      <c r="C57" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="E57" s="63" t="s">
-        <v>17</v>
-      </c>
-      <c r="F57" s="83" t="s">
+      <c r="E57" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="F57" s="71" t="s">
         <v>144</v>
       </c>
       <c r="G57" s="24" t="s">
@@ -6980,19 +6934,19 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="66.75">
-      <c r="A58" s="47" t="s">
+      <c r="A58" s="42" t="s">
         <v>206</v>
       </c>
-      <c r="B58" s="27" t="s">
+      <c r="B58" s="26" t="s">
         <v>207</v>
       </c>
-      <c r="C58" s="27" t="s">
+      <c r="C58" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="D58" s="60" t="s">
+      <c r="D58" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="E58" s="27" t="s">
+      <c r="E58" s="26" t="s">
         <v>12</v>
       </c>
       <c r="F58" s="22" t="s">
@@ -7009,16 +6963,16 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="66.75">
-      <c r="A59" s="47" t="s">
+      <c r="A59" s="42" t="s">
         <v>209</v>
       </c>
-      <c r="B59" s="27" t="s">
+      <c r="B59" s="26" t="s">
         <v>210</v>
       </c>
-      <c r="C59" s="27" t="s">
+      <c r="C59" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="D59" s="27" t="s">
+      <c r="D59" s="26" t="s">
         <v>212</v>
       </c>
       <c r="E59" s="26" t="s">
@@ -7038,16 +6992,16 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="66.75">
-      <c r="A60" s="47" t="s">
+      <c r="A60" s="42" t="s">
         <v>214</v>
       </c>
-      <c r="B60" s="27" t="s">
+      <c r="B60" s="26" t="s">
         <v>215</v>
       </c>
-      <c r="C60" s="27" t="s">
+      <c r="C60" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="D60" s="27" t="s">
+      <c r="D60" s="26" t="s">
         <v>212</v>
       </c>
       <c r="E60" s="26" t="s">
@@ -7067,16 +7021,16 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="66.75">
-      <c r="A61" s="47" t="s">
+      <c r="A61" s="42" t="s">
         <v>217</v>
       </c>
-      <c r="B61" s="27" t="s">
+      <c r="B61" s="26" t="s">
         <v>218</v>
       </c>
-      <c r="C61" s="27" t="s">
+      <c r="C61" s="26" t="s">
         <v>219</v>
       </c>
-      <c r="D61" s="27" t="s">
+      <c r="D61" s="26" t="s">
         <v>212</v>
       </c>
       <c r="E61" s="26" t="s">
@@ -7085,7 +7039,7 @@
       <c r="F61" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G61" s="97" t="s">
+      <c r="G61" s="82" t="s">
         <v>17</v>
       </c>
       <c r="H61" s="14" t="s">
@@ -7096,22 +7050,22 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="66.75">
-      <c r="A62" s="79" t="s">
+      <c r="A62" s="42" t="s">
         <v>220</v>
       </c>
-      <c r="B62" s="27" t="s">
+      <c r="B62" s="26" t="s">
         <v>221</v>
       </c>
-      <c r="C62" s="27" t="s">
+      <c r="C62" s="26" t="s">
         <v>222</v>
       </c>
-      <c r="D62" s="70" t="s">
+      <c r="D62" s="61" t="s">
         <v>212</v>
       </c>
-      <c r="E62" s="27" t="s">
+      <c r="E62" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="F62" s="69" t="s">
+      <c r="F62" s="60" t="s">
         <v>15</v>
       </c>
       <c r="G62" s="24" t="s">
@@ -7125,28 +7079,28 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="66.75">
-      <c r="A63" s="47" t="s">
+      <c r="A63" s="42" t="s">
         <v>224</v>
       </c>
-      <c r="B63" s="27" t="s">
+      <c r="B63" s="26" t="s">
         <v>225</v>
       </c>
-      <c r="C63" s="27" t="s">
+      <c r="C63" s="26" t="s">
         <v>226</v>
       </c>
-      <c r="D63" s="27" t="s">
+      <c r="D63" s="26" t="s">
         <v>227</v>
       </c>
       <c r="E63" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="F63" s="27" t="s">
+      <c r="F63" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G63" s="68" t="s">
+      <c r="G63" s="59" t="s">
         <v>228</v>
       </c>
-      <c r="H63" s="65" t="s">
+      <c r="H63" s="56" t="s">
         <v>229</v>
       </c>
       <c r="I63" s="19" t="s">
@@ -7154,28 +7108,28 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="66.75">
-      <c r="A64" s="47" t="s">
+      <c r="A64" s="42" t="s">
         <v>231</v>
       </c>
-      <c r="B64" s="27" t="s">
+      <c r="B64" s="26" t="s">
         <v>232</v>
       </c>
-      <c r="C64" s="27" t="s">
+      <c r="C64" s="26" t="s">
         <v>233</v>
       </c>
-      <c r="D64" s="27" t="s">
+      <c r="D64" s="26" t="s">
         <v>227</v>
       </c>
       <c r="E64" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="F64" s="27" t="s">
+      <c r="F64" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G64" s="68" t="s">
+      <c r="G64" s="59" t="s">
         <v>234</v>
       </c>
-      <c r="H64" s="65" t="s">
+      <c r="H64" s="56" t="s">
         <v>229</v>
       </c>
       <c r="I64" s="19" t="s">
@@ -7183,28 +7137,28 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="66.75">
-      <c r="A65" s="98" t="s">
+      <c r="A65" s="83" t="s">
         <v>235</v>
       </c>
-      <c r="B65" s="99" t="s">
+      <c r="B65" s="84" t="s">
         <v>236</v>
       </c>
-      <c r="C65" s="63" t="s">
+      <c r="C65" s="54" t="s">
         <v>237</v>
       </c>
-      <c r="D65" s="27" t="s">
+      <c r="D65" s="26" t="s">
         <v>227</v>
       </c>
       <c r="E65" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="F65" s="27" t="s">
+      <c r="F65" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="G65" s="68" t="s">
+      <c r="G65" s="59" t="s">
         <v>238</v>
       </c>
-      <c r="H65" s="65" t="s">
+      <c r="H65" s="56" t="s">
         <v>229</v>
       </c>
       <c r="I65" s="19" t="s">
